--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,112 +3165,112 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46142.875</v>
+        <v>46142.85416666666</v>
       </c>
     </row>
     <row r="31">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7249,27 +7249,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46142.89583333334</v>
+        <v>46142.875</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,112 +2771,112 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G34" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2723,22 +2723,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G35" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI35"/>
+  <dimension ref="A1:BI40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46142.5</v>
+        <v>46142.47916666666</v>
       </c>
     </row>
     <row r="10">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46142.5</v>
+        <v>46142.47916666666</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46142.5</v>
+        <v>46142.47916666666</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46142.54166666666</v>
+        <v>46142.47916666666</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46142.54166666666</v>
+        <v>46142.5</v>
       </c>
     </row>
     <row r="14">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46142.54166666666</v>
+        <v>46142.5</v>
       </c>
     </row>
     <row r="15">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3407,10 +3407,10 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46142.55555555555</v>
+        <v>46142.5</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.17</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>8.35</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>14.3</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46142.58333333334</v>
+        <v>46142.54166666666</v>
       </c>
     </row>
     <row r="17">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46142.58333333334</v>
+        <v>46142.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -3900,27 +3900,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46142.60416666666</v>
+        <v>46142.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,12 +4097,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46142.60416666666</v>
+        <v>46142.55555555555</v>
       </c>
     </row>
     <row r="20">
@@ -4294,27 +4294,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Feiha</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46142.625</v>
+        <v>46142.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSB Berkane</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kawkab Marrakech</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46142.66666666666</v>
+        <v>46142.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.60416666666</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.60416666666</v>
       </c>
     </row>
     <row r="24">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Al Feiha</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.625</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>RSB Berkane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Kawkab Marrakech</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.66666666666</v>
       </c>
     </row>
     <row r="26">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.46</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>5.14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.70833333334</v>
       </c>
     </row>
     <row r="27">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46142.79166666666</v>
+        <v>46142.72916666666</v>
       </c>
     </row>
     <row r="30">
@@ -6264,27 +6264,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46142.85416666666</v>
+        <v>46142.72916666666</v>
       </c>
     </row>
     <row r="31">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46142.875</v>
+        <v>46142.72916666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46142.875</v>
+        <v>46142.72916666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Jamaica Jamaica National Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46142.875</v>
+        <v>46142.72916666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46142.875</v>
+        <v>46142.79166666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,6 +7437,991 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
+        <v>46142.85416666666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Al Buqa'a</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI36" s="3" t="n">
+        <v>46142.875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Al Salt</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Al Wihdat</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N37" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI37" s="3" t="n">
+        <v>46142.875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Al Jazeera</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Shabab Al Ordon</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI38" s="3" t="n">
+        <v>46142.875</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Jordan Jordanian Pro League</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Al Faisaly</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Al Ramtha</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N39" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" s="3" t="n">
+        <v>46142.875</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Curicó Unido</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" s="3" t="n">
         <v>46142.875</v>
       </c>
     </row>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G39" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI40"/>
+  <dimension ref="A1:BI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Al Hussein</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.79166666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.85416666666</v>
       </c>
     </row>
     <row r="29">
@@ -6067,12 +6067,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="BI29" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.875</v>
       </c>
     </row>
     <row r="30">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6452,7 +6452,7 @@
         <v>0</v>
       </c>
       <c r="BI30" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.875</v>
       </c>
     </row>
     <row r="31">
@@ -6461,27 +6461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.875</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46142.72916666666</v>
+        <v>46142.875</v>
       </c>
     </row>
     <row r="33">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jamaica Jamaica National Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7043,1385 +7043,6 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46142.72916666666</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Sama Al Sarhan</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Al Hussein</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI34" s="3" t="n">
-        <v>46142.79166666666</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>All Boys</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>San Miguel</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI35" s="3" t="n">
-        <v>46142.85416666666</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Al Faisaly</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Al Ramtha</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="n">
-        <v>0</v>
-      </c>
-      <c r="T36" t="n">
-        <v>0</v>
-      </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
-      <c r="W36" t="n">
-        <v>0</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH36" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI36" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Al Ahli</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Al Buqa'a</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
-        <v>0</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
-      <c r="W37" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH37" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI37" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Al Jazeera</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Shabab Al Ordon</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="n">
-        <v>0</v>
-      </c>
-      <c r="T38" t="n">
-        <v>0</v>
-      </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
-      <c r="W38" t="n">
-        <v>0</v>
-      </c>
-      <c r="X38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH38" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI38" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Unión Española</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N39" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Al Salt</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Al Wihdat</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI40" s="3" t="n">
         <v>46142.875</v>
       </c>
     </row>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5962,10 +5962,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>6.13</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,79 +801,79 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,19 +915,19 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>6.13</v>
+        <v>1.76</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -810,16 +810,16 @@
         <v>3.6</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="T2" t="n">
         <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>4.38</v>
+        <v>3.8</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
         <v>2.88</v>
@@ -828,13 +828,13 @@
         <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
@@ -843,7 +843,7 @@
         <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
@@ -867,13 +867,13 @@
         <v>1.68</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
         <v>2.01</v>
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3568,124 +3568,124 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,112 +3756,112 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.76</v>
+        <v>6.13</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -3870,19 +3870,19 @@
         <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>6.13</v>
+        <v>1.76</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4750,70 +4750,70 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>5.67</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4947,70 +4947,70 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>7.31</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>5.23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>2.38</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.2</v>
       </c>
-      <c r="AD16" t="n">
-        <v>4.22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BC16" t="n">
-        <v>1.85</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.55</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.41</v>
       </c>
-      <c r="Q17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>0</v>
-      </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>6.13</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>6.13</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>4.03</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,112 +3953,112 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>6.13</v>
+        <v>1.76</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>8.35</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>14.3</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.35</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>14.3</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4750,70 +4750,70 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="U22" t="n">
-        <v>5.67</v>
+        <v>7.31</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.3</v>
+        <v>5.23</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4947,124 +4947,124 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>7.31</v>
+        <v>5.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="AE23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL23" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AM23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,112 +3559,112 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.41</v>
+        <v>3.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>6.13</v>
+        <v>1.76</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
         <v>0</v>
@@ -3673,19 +3673,19 @@
         <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.7</v>
+        <v>1.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.76</v>
+        <v>6.13</v>
       </c>
       <c r="S18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW18" t="n">
         <v>2.5</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW18" t="n">
+      <c r="AX18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.14</v>
+        <v>1.63</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.4</v>
+        <v>4.49</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.47</v>
+        <v>4.02</v>
       </c>
       <c r="R26" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="S26" t="n">
         <v>5.46</v>
@@ -5574,10 +5574,10 @@
         <v>3.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
         <v>3.08</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>1.85</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="U17" t="n">
-        <v>2.25</v>
+        <v>5.4</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.22</v>
+        <v>5.4</v>
       </c>
       <c r="AE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH17" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AI17" t="n">
-        <v>4.44</v>
+        <v>3.4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AL17" t="n">
         <v>2.23</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.23</v>
+        <v>2.6</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>1.27</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AR17" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.23</v>
+        <v>1.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.85</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.55</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>5.4</v>
+        <v>2.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.4</v>
+        <v>4.42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.29</v>
+        <v>2.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.35</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>14.3</v>
+        <v>14</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,16 +4371,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -4392,28 +4392,28 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,19 +4446,19 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB20" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -5144,124 +5144,124 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.96</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.67</v>
+        <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>4.67</v>
+        <v>4.2</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -813,10 +813,10 @@
         <v>2.38</v>
       </c>
       <c r="T2" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8</v>
+        <v>4.38</v>
       </c>
       <c r="V2" t="n">
         <v>1.33</v>
@@ -828,13 +828,13 @@
         <v>2.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AB2" t="n">
         <v>1</v>
@@ -858,7 +858,7 @@
         <v>1.31</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.35</v>
+        <v>5.6</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.09</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.39</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2.71</v>
+        <v>3.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.83</v>
+        <v>2.36</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>5.6</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU16" t="n">
         <v>3.2</v>
       </c>
-      <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.71</v>
-      </c>
       <c r="AV16" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.14</v>
+        <v>1.83</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.7</v>
+        <v>4.65</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>6.13</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.85</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AR17" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.71</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD17" t="n">
         <v>3.3</v>
       </c>
-      <c r="AW17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
       <c r="BE17" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>6.13</v>
       </c>
       <c r="S18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z18" t="n">
         <v>4.2</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AA18" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="AD18" t="n">
-        <v>4.33</v>
+        <v>5.4</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>2.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4371,16 +4371,16 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -4392,28 +4392,28 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,19 +4446,19 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4568,16 +4568,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -4589,28 +4589,28 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
@@ -4643,19 +4643,19 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>7.31</v>
+        <v>5.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="AE22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AM22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="U23" t="n">
-        <v>5.67</v>
+        <v>7.31</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="X23" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>5.23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -807,7 +807,7 @@
         <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="S2" t="n">
         <v>2.38</v>
@@ -831,7 +831,7 @@
         <v>1.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="AA2" t="n">
         <v>1.06</v>
@@ -846,10 +846,10 @@
         <v>3.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
         <v>3.02</v>
@@ -873,7 +873,7 @@
         <v>1.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AK16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AX16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.86</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>1.41</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>6.13</v>
       </c>
       <c r="S17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z17" t="n">
         <v>4.2</v>
       </c>
-      <c r="T17" t="n">
+      <c r="AA17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT17" t="n">
         <v>2.1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW17" t="n">
         <v>2.5</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM17" t="n">
+      <c r="AX17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>1.29</v>
       </c>
-      <c r="AN17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>6.13</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>1.85</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.8</v>
+        <v>2.38</v>
       </c>
       <c r="U18" t="n">
-        <v>5.4</v>
+        <v>2.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.4</v>
+        <v>4.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.02</v>
+        <v>2.54</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.4</v>
+        <v>4.42</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.26</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>2.55</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.27</v>
+        <v>1.49</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.44</v>
+        <v>1.81</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.71</v>
+        <v>2.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.3</v>
+        <v>2.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>2.5</v>
+        <v>1.84</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.98</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.29</v>
+        <v>2.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>4</v>
+        <v>1.75</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>2.1</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,37 +801,37 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.21</v>
       </c>
       <c r="R2" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="S2" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>4.38</v>
+        <v>3.94</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="X2" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>6.05</v>
+        <v>6.25</v>
       </c>
       <c r="AA2" t="n">
         <v>1.06</v>
@@ -840,91 +840,91 @@
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.02</v>
+        <v>3.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.6</v>
+        <v>5.83</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AK2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="BE2" t="n">
         <v>1.68</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.7</v>
       </c>
       <c r="BF2" t="n">
         <v>1.16</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,34 +4446,34 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,22 +4544,22 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>8.300000000000001</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4568,16 +4568,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -4589,28 +4589,28 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
         <v>0</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
@@ -4643,19 +4643,19 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
         <v>0</v>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S22" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="U22" t="n">
-        <v>5.67</v>
+        <v>7.31</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.3</v>
+        <v>5.23</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="T23" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="U23" t="n">
-        <v>7.31</v>
+        <v>5.67</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="AE23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL23" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AM23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY16" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
+      <c r="AZ16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>4.65</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>1.86</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.41</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>6.13</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.85</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AR17" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.71</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD17" t="n">
         <v>3.3</v>
       </c>
-      <c r="AW17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>0</v>
-      </c>
       <c r="BE17" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="T18" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="U18" t="n">
-        <v>2.15</v>
+        <v>6.13</v>
       </c>
       <c r="V18" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="W18" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="X18" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD18" t="n">
         <v>5.6</v>
       </c>
-      <c r="AA18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.33</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.62</v>
+        <v>1.38</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.22</v>
+        <v>2.59</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.42</v>
+        <v>3.34</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AK18" t="n">
         <v>1.57</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.55</v>
+        <v>2.23</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.2</v>
+        <v>2.68</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>1.27</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AU18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.84</v>
+        <v>2.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4356,70 +4356,70 @@
         <v>16</v>
       </c>
       <c r="S20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="T20" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>5.25</v>
+        <v>5.15</v>
       </c>
       <c r="X20" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Y20" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL20" t="n">
         <v>2.04</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.05</v>
       </c>
       <c r="AM20" t="n">
         <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4464,16 +4464,16 @@
         <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="BD20" t="n">
         <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.6</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.92</v>
+        <v>2.15</v>
       </c>
       <c r="T22" t="n">
-        <v>2.46</v>
+        <v>2.2</v>
       </c>
       <c r="U22" t="n">
-        <v>7.31</v>
+        <v>5.67</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.8</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.72</v>
+        <v>3.02</v>
       </c>
       <c r="AE22" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL22" t="n">
         <v>1.73</v>
       </c>
-      <c r="AF22" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="AJ22" t="n">
+      <c r="AM22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="S23" t="n">
-        <v>2.15</v>
+        <v>1.92</v>
       </c>
       <c r="T23" t="n">
-        <v>2.2</v>
+        <v>2.46</v>
       </c>
       <c r="U23" t="n">
-        <v>5.67</v>
+        <v>7.31</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="X23" t="n">
-        <v>2.9</v>
+        <v>2.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>5.8</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.02</v>
+        <v>3.72</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.06</v>
+        <v>1.73</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>2.01</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>5.23</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.1</v>
+        <v>2.65</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.23</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.49</v>
+        <v>7.55</v>
       </c>
       <c r="Q26" t="n">
         <v>4.02</v>
@@ -5577,7 +5577,7 @@
         <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
         <v>3.08</v>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
         <v>2.45</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -804,19 +804,19 @@
         <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="R2" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>2.58</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
-        <v>3.94</v>
+        <v>3.8</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -867,13 +867,13 @@
         <v>1.67</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AM2" t="n">
         <v>1.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="BC2" t="n">
         <v>2.03</v>
@@ -927,7 +927,7 @@
         <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.11</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>5.95</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3577,16 +3577,16 @@
         <v>2.15</v>
       </c>
       <c r="V16" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="X16" t="n">
         <v>2.36</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z16" t="n">
         <v>5.6</v>
@@ -3598,7 +3598,7 @@
         <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD16" t="n">
         <v>4.33</v>
@@ -3607,7 +3607,7 @@
         <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="AG16" t="n">
         <v>2.54</v>
@@ -3619,7 +3619,7 @@
         <v>4.42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AK16" t="n">
         <v>1.57</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,34 +4446,34 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
@@ -4643,34 +4643,34 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4750,16 +4750,16 @@
         <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="U22" t="n">
-        <v>5.67</v>
+        <v>5.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
         <v>2.75</v>
@@ -4768,7 +4768,7 @@
         <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
         <v>7.5</v>
@@ -4780,22 +4780,22 @@
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
         <v>7.3</v>
@@ -4810,10 +4810,10 @@
         <v>1.73</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.1</v>
+        <v>1.81</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="V23" t="n">
         <v>1.3</v>
       </c>
-      <c r="Q23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>8</v>
-      </c>
-      <c r="S23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U23" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.31</v>
-      </c>
       <c r="W23" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
         <v>2.01</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.23</v>
+        <v>5.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.82</v>
+        <v>1.77</v>
       </c>
       <c r="AM23" t="n">
         <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,16 +5052,16 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="BF23" t="n">
         <v>1.2</v>
@@ -5156,19 +5156,19 @@
         <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.35</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB24" t="n">
         <v>1</v>
@@ -5177,13 +5177,13 @@
         <v>1.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
         <v>2.97</v>
@@ -5192,10 +5192,10 @@
         <v>1.31</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
         <v>1.63</v>
@@ -5249,13 +5249,13 @@
         <v>2.08</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
         <v>1.71</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
         <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>1.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="T17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U17" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X17" t="n">
         <v>2.1</v>
       </c>
-      <c r="U17" t="n">
+      <c r="Y17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW17" t="n">
         <v>2.5</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ17" t="n">
+      <c r="AX17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
+      <c r="BC17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>5.65</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.4</v>
+        <v>4.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.85</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U18" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK18" t="n">
+      <c r="AL18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE18" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BF18" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7.55</v>
+        <v>4.4</v>
       </c>
       <c r="Q26" t="n">
         <v>4.02</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3571,10 +3571,10 @@
         <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="V16" t="n">
         <v>1.26</v>
@@ -3583,13 +3583,13 @@
         <v>3.32</v>
       </c>
       <c r="X16" t="n">
-        <v>2.36</v>
+        <v>2.23</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.08</v>
@@ -3601,28 +3601,28 @@
         <v>1.14</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.23</v>
+        <v>2.26</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.54</v>
+        <v>2.51</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.42</v>
+        <v>4.32</v>
       </c>
       <c r="AJ16" t="n">
         <v>1.19</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AL16" t="n">
         <v>2.55</v>
@@ -3631,7 +3631,7 @@
         <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3643,7 +3643,7 @@
         <v>1.49</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="AS16" t="n">
         <v>2.28</v>
@@ -3658,7 +3658,7 @@
         <v>2.33</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AX16" t="n">
         <v>1.52</v>
@@ -3676,16 +3676,16 @@
         <v>1.12</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.65</v>
+        <v>4.7</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.4</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.85</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="U17" t="n">
-        <v>6.13</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AK17" t="n">
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.57</v>
       </c>
-      <c r="AL17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.53</v>
+        <v>1.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="R18" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>1.85</v>
       </c>
       <c r="T18" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U18" t="n">
+        <v>6.13</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X18" t="n">
         <v>2.1</v>
       </c>
-      <c r="U18" t="n">
+      <c r="Y18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW18" t="n">
         <v>2.5</v>
       </c>
-      <c r="V18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AX18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW18" t="n">
+      <c r="BC18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>5.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="T22" t="n">
-        <v>2.19</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>5.6</v>
+        <v>6.63</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W22" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>2.43</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.9</v>
+        <v>3.73</v>
       </c>
       <c r="AE22" t="n">
-        <v>2.04</v>
+        <v>1.78</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.62</v>
+        <v>2.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.55</v>
+        <v>2.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>7.3</v>
+        <v>5.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK22" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.81</v>
+        <v>2.8</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="U23" t="n">
-        <v>6.63</v>
+        <v>5.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="X23" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
         <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.73</v>
+        <v>2.9</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.01</v>
+        <v>1.62</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.1</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5144,43 +5144,43 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
         <v>3</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
         <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
         <v>6.5</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB24" t="n">
         <v>1.05</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1</v>
       </c>
       <c r="AC24" t="n">
         <v>1.24</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>3.77</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
         <v>1.95</v>
@@ -5189,10 +5189,10 @@
         <v>2.97</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.08</v>
@@ -5216,31 +5216,31 @@
         <v>1.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AS24" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="AU24" t="n">
         <v>3.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AZ24" t="n">
         <v>1.95</v>
@@ -5249,7 +5249,7 @@
         <v>2.08</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
         <v>2.01</v>
@@ -5529,7 +5529,7 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.4</v>
+        <v>7.55</v>
       </c>
       <c r="Q26" t="n">
         <v>4.02</v>
@@ -5929,7 +5929,7 @@
         <v>2.45</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3953,22 +3953,22 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="R18" t="n">
         <v>5.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="U18" t="n">
-        <v>6.13</v>
+        <v>5.82</v>
       </c>
       <c r="V18" t="n">
         <v>1.2</v>
@@ -3986,7 +3986,7 @@
         <v>4.55</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AB18" t="n">
         <v>1</v>
@@ -4016,16 +4016,16 @@
         <v>1.24</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,25 +801,25 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>2.63</v>
       </c>
       <c r="T2" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
         <v>2.83</v>
@@ -840,10 +840,10 @@
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.62</v>
+        <v>3.34</v>
       </c>
       <c r="AE2" t="n">
         <v>1.83</v>
@@ -855,7 +855,7 @@
         <v>3.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
         <v>5.83</v>
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="BC2" t="n">
         <v>2.03</v>
@@ -927,7 +927,7 @@
         <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1601,25 +1601,25 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>3.06</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
         <v>2.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.95</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
         <v>1.04</v>
@@ -1628,40 +1628,40 @@
         <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.42</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
         <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>5.95</v>
+        <v>6.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
         <v>1.82</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1706,13 +1706,13 @@
         <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.03</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.92</v>
+        <v>3.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
         <v>1.14</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>1.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="U16" t="n">
-        <v>2.22</v>
+        <v>5.82</v>
       </c>
       <c r="V16" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="W16" t="n">
-        <v>3.32</v>
+        <v>3.68</v>
       </c>
       <c r="X16" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>4.55</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AD16" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.61</v>
+        <v>1.38</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.26</v>
+        <v>2.59</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.51</v>
+        <v>2.02</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.32</v>
+        <v>3.34</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AK16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR16" t="n">
         <v>1.44</v>
       </c>
-      <c r="AL16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AS16" t="n">
-        <v>2.28</v>
+        <v>1.71</v>
       </c>
       <c r="AT16" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="AU16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.33</v>
+        <v>3.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.3</v>
+        <v>1.62</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.7</v>
+        <v>5.65</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.88</v>
+        <v>2.16</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK17" t="n">
         <v>1.44</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AL17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
+      <c r="AZ17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC17" t="n">
         <v>1.83</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.36</v>
+        <v>4.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="U18" t="n">
-        <v>5.82</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>3.68</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF18" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AI18" t="n">
-        <v>3.34</v>
+        <v>6.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.57</v>
+        <v>1.26</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.71</v>
+        <v>2.83</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD18" t="n">
         <v>3.3</v>
       </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.65</v>
-      </c>
       <c r="BE18" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>10.48</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,34 +4446,34 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>9.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>5.15</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
@@ -4643,34 +4643,34 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>4.15</v>
       </c>
       <c r="S22" t="n">
-        <v>1.86</v>
+        <v>2.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="U22" t="n">
-        <v>6.63</v>
+        <v>4.6</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="W22" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.43</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="Z22" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="AB22" t="n">
         <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.73</v>
+        <v>2.9</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.78</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.01</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.85</v>
+        <v>3.55</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.1</v>
+        <v>7.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.8</v>
+        <v>1.81</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
       <c r="Q23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD23" t="n">
         <v>3.6</v>
       </c>
-      <c r="R23" t="n">
-        <v>5</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="U23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y23" t="n">
+      <c r="AE23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>5.05</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5144,13 +5144,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.9</v>
+        <v>3.12</v>
       </c>
       <c r="T24" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
@@ -5159,19 +5159,19 @@
         <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA24" t="n">
         <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
         <v>1.24</v>
@@ -5183,13 +5183,13 @@
         <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AG24" t="n">
         <v>2.97</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
         <v>6.1</v>
@@ -5198,16 +5198,16 @@
         <v>1.08</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5219,7 +5219,7 @@
         <v>1.42</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS24" t="n">
         <v>2.17</v>
@@ -5231,10 +5231,10 @@
         <v>3.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AX24" t="n">
         <v>1.61</v>
@@ -5249,19 +5249,19 @@
         <v>2.08</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>7.55</v>
+        <v>2.35</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.02</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
         <v>5.46</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Curicó Unido</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -807,19 +807,19 @@
         <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="S2" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>3.87</v>
+        <v>3.41</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W2" t="n">
         <v>2.83</v>
@@ -846,19 +846,19 @@
         <v>3.34</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>3.11</v>
+        <v>2.97</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.83</v>
+        <v>5.5</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.08</v>
@@ -870,10 +870,10 @@
         <v>2.05</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -927,7 +927,7 @@
         <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1401,70 +1401,70 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1598,70 +1598,70 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>3.32</v>
+        <v>2.5</v>
       </c>
       <c r="X17" t="n">
-        <v>2.36</v>
+        <v>3.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>5.55</v>
+        <v>7</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="AD17" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.53</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.37</v>
+        <v>6.25</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AM17" t="n">
         <v>1.22</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.49</v>
+        <v>1.7</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.81</v>
+        <v>2.54</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.28</v>
+        <v>2.83</v>
       </c>
       <c r="AT17" t="n">
-        <v>3</v>
+        <v>4.03</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.33</v>
+        <v>2.03</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>1.34</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.2</v>
+        <v>3.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.53</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AK18" t="n">
         <v>1.44</v>
       </c>
-      <c r="W18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AL18" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AM18" t="n">
         <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.26</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>1.49</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.54</v>
+        <v>1.81</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.83</v>
+        <v>2.28</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.03</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.03</v>
+        <v>2.33</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.34</v>
+        <v>1.52</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>10.48</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,34 +4446,34 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>10.48</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
@@ -4643,34 +4643,34 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.67</v>
+        <v>1.36</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>4.15</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="T22" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="V22" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="W22" t="n">
-        <v>2.55</v>
+        <v>2.91</v>
       </c>
       <c r="X22" t="n">
-        <v>2.9</v>
+        <v>2.53</v>
       </c>
       <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.34</v>
       </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI22" t="n">
-        <v>7.3</v>
+        <v>5.05</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.23</v>
+        <v>1.95</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>4.15</v>
       </c>
       <c r="S23" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W23" t="n">
-        <v>2.91</v>
+        <v>2.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.85</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.25</v>
       </c>
-      <c r="AD23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AI23" t="n">
-        <v>5.05</v>
+        <v>7.3</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.64</v>
+        <v>1.81</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.95</v>
+        <v>2.23</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>2.91</v>
+        <v>3.1</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>2.46</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="U2" t="n">
-        <v>3.41</v>
+        <v>3.88</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -849,7 +849,7 @@
         <v>1.85</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AG2" t="n">
         <v>2.97</v>
@@ -858,7 +858,7 @@
         <v>1.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.08</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1407,7 +1407,7 @@
         <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="V5" t="n">
         <v>1.35</v>
@@ -1422,7 +1422,7 @@
         <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="AA5" t="n">
         <v>1.04</v>
@@ -1440,7 +1440,7 @@
         <v>1.85</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AG5" t="n">
         <v>3.16</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.36</v>
+        <v>4.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.75</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>5.5</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>1.89</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="U16" t="n">
-        <v>5.82</v>
+        <v>2.5</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>3.68</v>
+        <v>2.5</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.55</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AD16" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="AE16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.38</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AI16" t="n">
-        <v>3.34</v>
+        <v>6.25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.55</v>
+        <v>1.85</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.27</v>
+        <v>1.83</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.57</v>
+        <v>1.26</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.71</v>
+        <v>2.83</v>
       </c>
       <c r="AT16" t="n">
-        <v>2.1</v>
+        <v>4.03</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AV16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.3</v>
       </c>
-      <c r="AW16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>5.65</v>
-      </c>
       <c r="BE16" t="n">
-        <v>2.16</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.67</v>
+        <v>5.5</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>1.89</v>
       </c>
       <c r="T17" t="n">
-        <v>2.28</v>
+        <v>2.47</v>
       </c>
       <c r="U17" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW17" t="n">
         <v>2.5</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
+      <c r="AX17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>5.65</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.32</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Shabab Al Ordon</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Shabab Al Ordon</t>
         </is>
       </c>
       <c r="G33" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.51</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,79 +1589,79 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,19 +1703,19 @@
         <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3568,10 +3568,10 @@
         <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.28</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
         <v>2.5</v>
@@ -3628,10 +3628,10 @@
         <v>1.83</v>
       </c>
       <c r="AM16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN16" t="n">
         <v>1.22</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.26</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.89</v>
+        <v>3.68</v>
       </c>
       <c r="T17" t="n">
-        <v>2.47</v>
+        <v>2.29</v>
       </c>
       <c r="U17" t="n">
-        <v>5.82</v>
+        <v>2.22</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
-        <v>3.68</v>
+        <v>3.32</v>
       </c>
       <c r="X17" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.55</v>
+        <v>5.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="AD17" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.59</v>
+        <v>2.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.02</v>
+        <v>2.53</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="AI17" t="n">
-        <v>3.34</v>
+        <v>4.37</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="AL17" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AM17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.13</v>
       </c>
-      <c r="AN17" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BC17" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.65</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.16</v>
+        <v>1.87</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="S18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W18" t="n">
         <v>3.68</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.32</v>
-      </c>
       <c r="X18" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.55</v>
+        <v>4.55</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AD18" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AE18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>2.35</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.2</v>
+        <v>5.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>10.48</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>4.27</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4431,13 +4431,13 @@
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AU20" t="n">
         <v>0</v>
@@ -4446,34 +4446,34 @@
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,79 +4544,79 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>10.48</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>4.27</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
@@ -4628,13 +4628,13 @@
         <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
         <v>0</v>
@@ -4643,34 +4643,34 @@
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Faisaly</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Ramtha</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Faisaly</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Al Ramtha</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G32" t="n">

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI33"/>
+  <dimension ref="A1:BI28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,19 +801,19 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="T2" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U2" t="n">
         <v>3.88</v>
@@ -840,19 +840,19 @@
         <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.34</v>
+        <v>3.55</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AH2" t="n">
         <v>1.3</v>
@@ -870,49 +870,49 @@
         <v>2.05</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB2" t="n">
         <v>1.19</v>
@@ -921,7 +921,7 @@
         <v>2.03</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="BE2" t="n">
         <v>1.68</v>
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1392,79 +1392,79 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
@@ -1506,19 +1506,19 @@
         <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,16 +1589,16 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
         <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="T6" t="n">
         <v>2.25</v>
@@ -1625,13 +1625,13 @@
         <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
         <v>1.28</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.51</v>
+        <v>3.34</v>
       </c>
       <c r="AE6" t="n">
         <v>1.85</v>
@@ -1652,55 +1652,55 @@
         <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AL6" t="n">
         <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.07</v>
+        <v>1.29</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB6" t="n">
         <v>1.18</v>
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.83</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U16" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="X16" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AA16" t="n">
         <v>1.07</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AI16" t="n">
-        <v>6.25</v>
+        <v>4.7</v>
       </c>
       <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BB16" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC16" t="n">
-        <v>2.25</v>
+        <v>1.86</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.57</v>
+        <v>1.84</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>3.68</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="V17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN17" t="n">
         <v>1.26</v>
       </c>
-      <c r="W17" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="R18" t="n">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="S18" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="T18" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>5.82</v>
+        <v>6.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W18" t="n">
-        <v>3.68</v>
+        <v>3.76</v>
       </c>
       <c r="X18" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.55</v>
+        <v>4.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AD18" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AN18" t="n">
-        <v>2.57</v>
+        <v>2.89</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
         <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="BD18" t="n">
         <v>5.65</v>
@@ -4079,7 +4079,7 @@
         <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,130 +4347,130 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>12</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="V20" t="n">
         <v>1.14</v>
       </c>
-      <c r="Q20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="R20" t="n">
-        <v>16</v>
-      </c>
-      <c r="S20" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10.48</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.11</v>
-      </c>
       <c r="W20" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="X20" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.01</v>
+        <v>2.21</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.27</v>
+        <v>4.05</v>
       </c>
       <c r="AG20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1.63</v>
       </c>
-      <c r="AH20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.51</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.9</v>
+        <v>6.95</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.62</v>
+        <v>1.84</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.97</v>
+        <v>2.04</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
       <c r="BB20" t="n">
         <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BD20" t="n">
         <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="BF20" t="n">
         <v>1.57</v>
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
         <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
-        <v>2.91</v>
+        <v>2.96</v>
       </c>
       <c r="X22" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
         <v>1.01</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.96</v>
+        <v>2.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM22" t="n">
         <v>1.14</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4858,16 +4858,16 @@
         <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.95</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4938,76 +4938,76 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
         <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="S23" t="n">
         <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>4.6</v>
+        <v>5.43</v>
       </c>
       <c r="V23" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="W23" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="X23" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AE23" t="n">
         <v>2.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>7.3</v>
+        <v>6.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AN23" t="n">
         <v>1.81</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S24" t="n">
         <v>3.12</v>
       </c>
       <c r="T24" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="U24" t="n">
-        <v>2.87</v>
+        <v>3.05</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
@@ -5159,10 +5159,10 @@
         <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
         <v>6.3</v>
@@ -5171,22 +5171,22 @@
         <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AF24" t="n">
         <v>1.94</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.97</v>
+        <v>3.1</v>
       </c>
       <c r="AH24" t="n">
         <v>1.32</v>
@@ -5204,10 +5204,10 @@
         <v>2.14</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5216,43 +5216,43 @@
         <v>1.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.62</v>
+        <v>1.96</v>
       </c>
       <c r="AS24" t="n">
         <v>2.17</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.9</v>
+        <v>2.83</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.7</v>
+        <v>3.56</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AW24" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="AX24" t="n">
         <v>1.61</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AZ24" t="n">
         <v>1.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="n">
         <v>3.95</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>2.83</v>
       </c>
       <c r="R26" t="n">
-        <v>1.56</v>
+        <v>3.33</v>
       </c>
       <c r="S26" t="n">
         <v>5.46</v>
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Hussein</t>
+          <t>San Miguel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>4.41</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5765,16 +5765,16 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46142.79166666666</v>
+        <v>46142.85416666666</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>San Miguel</t>
+          <t>Curicó Unido</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -5962,10 +5962,10 @@
         <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -6058,991 +6058,6 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46142.85416666666</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Chile Primera B</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Unión Española</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Curicó Unido</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI29" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Al Salt</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Al Wihdat</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI30" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Al Faisaly</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Al Ramtha</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI31" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Al Ahli</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Al Buqa'a</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI32" s="3" t="n">
-        <v>46142.875</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="n">
-        <v>46142</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Jordan Jordanian Pro League</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Al Jazeera</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Shabab Al Ordon</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI33" s="3" t="n">
         <v>46142.875</v>
       </c>
     </row>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,7 +801,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.1</v>
+        <v>1.88</v>
       </c>
       <c r="Q2" t="n">
         <v>3.25</v>
@@ -846,10 +846,10 @@
         <v>3.55</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AG2" t="n">
         <v>3</v>
@@ -927,7 +927,7 @@
         <v>1.68</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.79</v>
+        <v>2.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2.82</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.75</v>
+        <v>3.12</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.4</v>
+        <v>1.31</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
         <v>2.88</v>
       </c>
       <c r="R5" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="S5" t="n">
         <v>3.02</v>
@@ -1416,7 +1416,7 @@
         <v>2.22</v>
       </c>
       <c r="X5" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="Y5" t="n">
         <v>1.19</v>
@@ -1443,10 +1443,10 @@
         <v>1.38</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AI5" t="n">
         <v>11</v>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
         <v>1.61</v>
@@ -1604,19 +1604,19 @@
         <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>3.03</v>
       </c>
       <c r="X6" t="n">
         <v>2.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
         <v>7.1</v>
@@ -1625,7 +1625,7 @@
         <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
         <v>1.28</v>
@@ -1658,7 +1658,7 @@
         <v>1.85</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
         <v>1.1</v>
@@ -1679,10 +1679,10 @@
         <v>2.19</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="AV6" t="n">
         <v>2.54</v>
@@ -1694,7 +1694,7 @@
         <v>1.59</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AZ6" t="n">
         <v>2.96</v>
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="R7" t="n">
-        <v>2.74</v>
+        <v>2.63</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2225,10 +2225,10 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2619,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.79</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U22" t="n">
-        <v>6.5</v>
+        <v>5.43</v>
       </c>
       <c r="V22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.32</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AD22" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AE22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.1</v>
+        <v>6.75</v>
       </c>
       <c r="AJ22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF22" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="S23" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="U23" t="n">
-        <v>5.43</v>
+        <v>6.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X23" t="n">
         <v>2.59</v>
       </c>
-      <c r="X23" t="n">
-        <v>3.05</v>
-      </c>
       <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI23" t="n">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -998,25 +998,25 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="S3" t="n">
-        <v>4.74</v>
+        <v>4.6</v>
       </c>
       <c r="T3" t="n">
         <v>1.65</v>
       </c>
       <c r="U3" t="n">
-        <v>3.42</v>
+        <v>3.36</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
         <v>1.98</v>
@@ -1028,7 +1028,7 @@
         <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
@@ -1037,10 +1037,10 @@
         <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="AE3" t="n">
         <v>3.12</v>
@@ -1049,28 +1049,28 @@
         <v>1.31</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.15</v>
+        <v>6.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AM3" t="n">
         <v>1.41</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>4.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>3.25</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>3.02</v>
+        <v>5.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>4.46</v>
+        <v>2.17</v>
       </c>
       <c r="V5" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="W5" t="n">
-        <v>2.22</v>
+        <v>3.03</v>
       </c>
       <c r="X5" t="n">
-        <v>3.75</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>9.4</v>
+        <v>7.1</v>
       </c>
       <c r="AA5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB5" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AC5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>1.06</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AK5" t="n">
-        <v>2.16</v>
+        <v>1.82</v>
       </c>
       <c r="AL5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX5" t="n">
         <v>1.59</v>
       </c>
-      <c r="AM5" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.79</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.75</v>
+        <v>3.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>3.02</v>
       </c>
       <c r="S6" t="n">
-        <v>5.36</v>
+        <v>3.46</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.17</v>
+        <v>4.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>3.03</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>2.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>3.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.16</v>
+        <v>4.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.1</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.3</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>2.63</v>
+        <v>2.73</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>4.14</v>
       </c>
       <c r="T7" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>3.62</v>
+        <v>3.32</v>
       </c>
       <c r="V7" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W7" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="X7" t="n">
-        <v>3.48</v>
+        <v>3.76</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z7" t="n">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AC7" t="n">
         <v>1.44</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AI7" t="n">
-        <v>11</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AL7" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
         <v>1.39</v>
       </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.35</v>
-      </c>
       <c r="BC7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BD7" t="n">
         <v>2.63</v>
       </c>
-      <c r="BD7" t="n">
-        <v>2.79</v>
-      </c>
       <c r="BE7" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,79 +2968,79 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>4.68</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>4.68</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3562,37 +3562,37 @@
         <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="R16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="S16" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X16" t="n">
         <v>2.38</v>
       </c>
-      <c r="U16" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Y16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
         <v>1.04</v>
@@ -3601,37 +3601,37 @@
         <v>1.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.16</v>
+        <v>2.3</v>
       </c>
       <c r="AG16" t="n">
-        <v>2.59</v>
+        <v>2.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AI16" t="n">
-        <v>4.7</v>
+        <v>4.25</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AL16" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>2.19</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.33</v>
+        <v>2.45</v>
       </c>
       <c r="AT16" t="n">
         <v>3.21</v>
@@ -3661,31 +3661,31 @@
         <v>1.82</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AY16" t="n">
         <v>1.28</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="BB16" t="n">
         <v>1.13</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.5</v>
+        <v>4.55</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.67</v>
       </c>
-      <c r="S17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U17" t="n">
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW17" t="n">
         <v>2.5</v>
       </c>
-      <c r="V17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="AX17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.4</v>
+        <v>4.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.5</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
-        <v>5.25</v>
+        <v>1.67</v>
       </c>
       <c r="S18" t="n">
-        <v>1.79</v>
+        <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="U18" t="n">
-        <v>6.44</v>
+        <v>2.5</v>
       </c>
       <c r="V18" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="W18" t="n">
-        <v>3.76</v>
+        <v>2.5</v>
       </c>
       <c r="X18" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.67</v>
       </c>
-      <c r="Z18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AF18" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.35</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,22 +4347,22 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="S20" t="n">
         <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>3.58</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
-        <v>10.7</v>
+        <v>10</v>
       </c>
       <c r="V20" t="n">
         <v>1.14</v>
@@ -4371,55 +4371,55 @@
         <v>5</v>
       </c>
       <c r="X20" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.21</v>
+        <v>2.05</v>
       </c>
       <c r="Z20" t="n">
         <v>3.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AB20" t="n">
         <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AD20" t="n">
         <v>9.1</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="AG20" t="n">
         <v>1.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.95</v>
+        <v>5.75</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,7 +4428,7 @@
         <v>1.2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AR20" t="n">
         <v>1.84</v>
@@ -4452,13 +4452,13 @@
         <v>1.69</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="BB20" t="n">
         <v>1.05</v>
@@ -4473,7 +4473,7 @@
         <v>2.81</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="S22" t="n">
-        <v>2.28</v>
+        <v>1.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="U22" t="n">
-        <v>5.43</v>
+        <v>6.5</v>
       </c>
       <c r="V22" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.59</v>
       </c>
-      <c r="X22" t="n">
-        <v>3.05</v>
-      </c>
       <c r="Y22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z22" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AI22" t="n">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.81</v>
+        <v>2.66</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="R23" t="n">
-        <v>7</v>
+        <v>4.33</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="U23" t="n">
-        <v>6.5</v>
+        <v>5.43</v>
       </c>
       <c r="V23" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.32</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AD23" t="n">
-        <v>3.7</v>
+        <v>2.88</v>
       </c>
       <c r="AE23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG23" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.1</v>
+        <v>6.75</v>
       </c>
       <c r="AJ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF23" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5135,22 +5135,22 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="S24" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
@@ -5159,19 +5159,19 @@
         <v>2.91</v>
       </c>
       <c r="X24" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
         <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
         <v>1.22</v>
@@ -5180,31 +5180,31 @@
         <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
         <v>3.1</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>6.1</v>
+        <v>5.4</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
         <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN24" t="n">
         <v>1.46</v>
@@ -5729,10 +5729,10 @@
         <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="R27" t="n">
-        <v>4.41</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5923,79 +5923,79 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
@@ -6037,19 +6037,19 @@
         <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,22 +801,22 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="S2" t="n">
         <v>2.64</v>
       </c>
       <c r="T2" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -837,43 +837,43 @@
         <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.55</v>
+        <v>5.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AL2" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>1.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
@@ -885,10 +885,10 @@
         <v>1.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="AT2" t="n">
         <v>3.74</v>
@@ -900,34 +900,34 @@
         <v>2.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AY2" t="n">
         <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="BA2" t="n">
         <v>2.72</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.03</v>
+        <v>2.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>3.02</v>
       </c>
       <c r="S5" t="n">
-        <v>5.36</v>
+        <v>3.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.17</v>
+        <v>4.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.36</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
-        <v>3.03</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>4.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.1</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>2.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.85</v>
+        <v>3.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.84</v>
+        <v>1.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.16</v>
+        <v>4.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.82</v>
+        <v>2.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>1.51</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.2</v>
+        <v>1.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.1</v>
+        <v>1.41</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AZ5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>5.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>3.02</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>3.46</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>2.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.53</v>
+        <v>3.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1983,22 +1983,22 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.85</v>
+        <v>4.46</v>
       </c>
       <c r="Q8" t="n">
         <v>3.25</v>
       </c>
       <c r="R8" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="S8" t="n">
-        <v>4.83</v>
+        <v>5.59</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U8" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="V8" t="n">
         <v>1.44</v>
@@ -2007,55 +2007,55 @@
         <v>2.47</v>
       </c>
       <c r="X8" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="Y8" t="n">
         <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="AA8" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB8" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.04</v>
       </c>
       <c r="AC8" t="n">
         <v>1.33</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AF8" t="n">
         <v>1.66</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="AH8" t="n">
         <v>1.19</v>
       </c>
       <c r="AI8" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,19 +2097,19 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BC8" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.28</v>
+        <v>3.34</v>
       </c>
       <c r="BE8" t="n">
         <v>1.52</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,34 +2180,34 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="T9" t="n">
         <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="V9" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
         <v>11.5</v>
@@ -2216,7 +2216,7 @@
         <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC9" t="n">
         <v>1.61</v>
@@ -2225,31 +2225,31 @@
         <v>2.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
         <v>1.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.15</v>
+        <v>5.65</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN9" t="n">
         <v>1.37</v>
@@ -2294,16 +2294,16 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
         <v>1.04</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,133 +2377,133 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R10" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U10" t="n">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="X10" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF10" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,80 +2574,80 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="U11" t="n">
-        <v>5.94</v>
+        <v>4.25</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W11" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X11" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AE11" t="n">
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN11" t="n">
         <v>1.48</v>
       </c>
-      <c r="AG11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="S12" t="n">
-        <v>3.48</v>
+        <v>2.44</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="U12" t="n">
-        <v>3.78</v>
+        <v>5.94</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="X12" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.65</v>
+        <v>4.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AI12" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BC12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD12" t="n">
         <v>2.88</v>
       </c>
-      <c r="BD12" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BE12" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.3</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.55</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="R18" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="S18" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.28</v>
+        <v>2.44</v>
       </c>
       <c r="U18" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="W18" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="X18" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.75</v>
+        <v>4.25</v>
       </c>
       <c r="AJ18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="BC18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.25</v>
-      </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>4.55</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4153,76 +4153,76 @@
         <v>1.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R19" t="n">
-        <v>6.25</v>
+        <v>8.15</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE19" t="n">
         <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4267,13 +4267,13 @@
         <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BD19" t="n">
         <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.11</v>
+        <v>2.05</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>13</v>
+        <v>3.49</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>4.82</v>
       </c>
       <c r="V20" t="n">
-        <v>1.14</v>
+        <v>1.57</v>
       </c>
       <c r="W20" t="n">
-        <v>5</v>
+        <v>2.31</v>
       </c>
       <c r="X20" t="n">
-        <v>1.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.75</v>
+        <v>1.62</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>2.88</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.81</v>
+        <v>1.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.8</v>
+        <v>2.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.32</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>2.96</v>
+        <v>2.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="AE22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AF22" t="n">
         <v>1.72</v>
       </c>
-      <c r="AF22" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG22" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.1</v>
+        <v>6.65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.66</v>
+        <v>1.96</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
-        <v>4.33</v>
+        <v>6</v>
       </c>
       <c r="S23" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="T23" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>5.43</v>
+        <v>6.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>2.59</v>
+        <v>2.95</v>
       </c>
       <c r="X23" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.88</v>
+        <v>3.7</v>
       </c>
       <c r="AE23" t="n">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" t="n">
-        <v>6.75</v>
+        <v>5.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL23" t="n">
         <v>1.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.24</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>5.41</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>7.07</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.38</v>
+        <v>4.41</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.83</v>
+        <v>2.63</v>
       </c>
       <c r="R26" t="n">
-        <v>3.33</v>
+        <v>1.62</v>
       </c>
       <c r="S26" t="n">
         <v>5.46</v>
@@ -5577,7 +5577,7 @@
         <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AG26" t="n">
         <v>3.08</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="T11" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>4.25</v>
+        <v>5.94</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AE11" t="n">
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,80 +2771,80 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="S12" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
-        <v>5.94</v>
+        <v>4.25</v>
       </c>
       <c r="V12" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W12" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X12" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AE12" t="n">
         <v>2.5</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN12" t="n">
         <v>1.48</v>
       </c>
-      <c r="AG12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AO12" t="n">
         <v>0</v>
       </c>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85</v>
+        <v>3.67</v>
       </c>
       <c r="T13" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4.68</v>
+        <v>3.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="X13" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BC13" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>3.54</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="U14" t="n">
         <v>4.11</v>
@@ -3198,10 +3198,10 @@
         <v>13</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AC14" t="n">
         <v>1.56</v>
@@ -3213,13 +3213,13 @@
         <v>2.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="AI14" t="n">
         <v>10.5</v>
@@ -3228,10 +3228,10 @@
         <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AM14" t="n">
         <v>1.36</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,79 +3362,79 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.87</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.87</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>2.37</v>
+        <v>3.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3.93</v>
+        <v>2.85</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>3.17</v>
+        <v>4.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="W15" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z15" t="n">
         <v>9</v>
       </c>
       <c r="AA15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.03</v>
       </c>
-      <c r="AB15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.93</v>
+        <v>2.13</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.31</v>
+        <v>1.58</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.46</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
+      <c r="AQ16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.21</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
         <v>7</v>
       </c>
-      <c r="S17" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF17" t="n">
         <v>2</v>
       </c>
-      <c r="Y17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AG17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.9</v>
+        <v>1.36</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
-        <v>1.81</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA18" t="n">
         <v>4</v>
       </c>
-      <c r="T18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.65</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.55</v>
+        <v>5.8</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
         <v>3</v>
@@ -4365,10 +4365,10 @@
         <v>4.82</v>
       </c>
       <c r="V20" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="X20" t="n">
         <v>3.5</v>
@@ -4395,7 +4395,7 @@
         <v>2.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AG20" t="n">
         <v>4.75</v>
@@ -4404,7 +4404,7 @@
         <v>1.12</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AJ20" t="n">
         <v>1</v>
@@ -4413,10 +4413,10 @@
         <v>2.14</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AN20" t="n">
         <v>1.62</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="U22" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="V22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.36</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI22" t="n">
-        <v>6.65</v>
+        <v>5.1</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.96</v>
+        <v>2.64</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="U23" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W23" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="X23" t="n">
-        <v>2.4</v>
+        <v>3.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.1</v>
+        <v>6.65</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.64</v>
+        <v>1.96</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5156,25 +5156,25 @@
         <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>2.91</v>
+        <v>3.14</v>
       </c>
       <c r="X24" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="Y24" t="n">
         <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="AA24" t="n">
         <v>1.06</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AD24" t="n">
         <v>3.5</v>
@@ -5186,16 +5186,16 @@
         <v>1.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.4</v>
+        <v>5.47</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK24" t="n">
         <v>1.62</v>
@@ -5216,37 +5216,37 @@
         <v>1.2</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.83</v>
+        <v>2.55</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AZ24" t="n">
         <v>1.95</v>
       </c>
       <c r="BA24" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="BB24" t="n">
         <v>1.2</v>
@@ -5258,7 +5258,7 @@
         <v>3.95</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="BF24" t="n">
         <v>1.16</v>
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="R25" t="n">
-        <v>5.41</v>
+        <v>5.25</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="T25" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>7.07</v>
+        <v>6.91</v>
       </c>
       <c r="V25" t="n">
         <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="X25" t="n">
         <v>3.2</v>
@@ -5371,40 +5371,40 @@
         <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AD25" t="n">
         <v>2.62</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AH25" t="n">
         <v>1.15</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AL25" t="n">
         <v>1.56</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>5.18</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>3.02</v>
+        <v>1.61</v>
       </c>
       <c r="S5" t="n">
-        <v>3.46</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="U5" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>4.2</v>
+        <v>2.73</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA5" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
       <c r="BB5" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.53</v>
+        <v>3.86</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>5.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>3.02</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3.46</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>2.04</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>2.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.9</v>
+        <v>3.12</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.16</v>
+        <v>4.7</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.1</v>
+        <v>17</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>3.04</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.86</v>
+        <v>2.53</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="S9" t="n">
-        <v>3.48</v>
+        <v>2.44</v>
       </c>
       <c r="T9" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>3.78</v>
+        <v>5.94</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="X9" t="n">
-        <v>3.92</v>
+        <v>3.42</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.65</v>
+        <v>4.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>9.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.37</v>
+        <v>1.87</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BC9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BD9" t="n">
         <v>2.88</v>
       </c>
-      <c r="BD9" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="S10" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>3.74</v>
+        <v>4.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK10" t="n">
         <v>2.11</v>
       </c>
-      <c r="X10" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.27</v>
-      </c>
       <c r="AL10" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.97</v>
+        <v>2.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="T11" t="n">
         <v>1.75</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="U11" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE11" t="n">
         <v>3</v>
       </c>
-      <c r="R11" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U11" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="AF11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1.55</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="X11" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AM11" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.87</v>
+        <v>1.37</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.33</v>
       </c>
-      <c r="BC11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.41</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,133 +2771,133 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3.52</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>4.25</v>
+        <v>3.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="W12" t="n">
-        <v>2.22</v>
+        <v>2.11</v>
       </c>
       <c r="X12" t="n">
-        <v>3.58</v>
+        <v>4.1</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF12" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R13" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U13" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK13" t="n">
         <v>2.25</v>
       </c>
-      <c r="S13" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U13" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="V13" t="n">
+      <c r="AL13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.4</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA13" t="n">
+      <c r="BC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="S14" t="n">
-        <v>3.54</v>
+        <v>3.67</v>
       </c>
       <c r="T14" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="U14" t="n">
-        <v>4.11</v>
+        <v>3.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>2.13</v>
+        <v>2.73</v>
       </c>
       <c r="X14" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.17</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.11</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.56</v>
+        <v>1.27</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.15</v>
+        <v>3.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.88</v>
+        <v>1.84</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.7</v>
+        <v>3.14</v>
       </c>
       <c r="AH14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.07</v>
       </c>
-      <c r="AI14" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
       <c r="AK14" t="n">
-        <v>2.25</v>
+        <v>1.71</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>1.36</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.67</v>
       </c>
-      <c r="S17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AD17" t="n">
-        <v>3.8</v>
+        <v>5.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="AF17" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.38</v>
+        <v>1.74</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.17</v>
+        <v>2.89</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.54</v>
+        <v>1.44</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.83</v>
+        <v>1.71</v>
       </c>
       <c r="AT17" t="n">
-        <v>4.03</v>
+        <v>2.1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.03</v>
+        <v>3.3</v>
       </c>
       <c r="AW17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AY17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.36</v>
+        <v>4.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>3.55</v>
       </c>
       <c r="R18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z18" t="n">
         <v>7</v>
       </c>
-      <c r="S18" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF18" t="n">
         <v>2</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AG18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.3</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R20" t="n">
-        <v>3.49</v>
+        <v>13</v>
       </c>
       <c r="S20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W20" t="n">
+        <v>5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AV20" t="n">
         <v>2.8</v>
       </c>
-      <c r="T20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.88</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.4</v>
+        <v>2.81</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>13</v>
+        <v>3.49</v>
       </c>
       <c r="S21" t="n">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="T21" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="U21" t="n">
-        <v>10</v>
+        <v>4.82</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="W21" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="X21" t="n">
-        <v>1.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="AN21" t="n">
-        <v>5.75</v>
+        <v>1.62</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.8</v>
+        <v>2.88</v>
       </c>
       <c r="BE21" t="n">
-        <v>2.81</v>
+        <v>1.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>5.18</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>3.02</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3.46</v>
       </c>
       <c r="T5" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.68</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>2.73</v>
+        <v>4.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.34</v>
+        <v>2.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.9</v>
+        <v>3.12</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.9</v>
+        <v>1.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.16</v>
+        <v>4.7</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.28</v>
+        <v>1.05</v>
       </c>
       <c r="AI5" t="n">
-        <v>6.1</v>
+        <v>17</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.8</v>
+        <v>2.34</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.83</v>
+        <v>1.51</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.15</v>
+        <v>1.41</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.54</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.05</v>
+        <v>3.04</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.86</v>
+        <v>2.53</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>5.18</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.75</v>
+        <v>3.75</v>
       </c>
       <c r="R6" t="n">
-        <v>3.02</v>
+        <v>1.61</v>
       </c>
       <c r="S6" t="n">
-        <v>3.46</v>
+        <v>5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>4.1</v>
+        <v>2.22</v>
       </c>
       <c r="V6" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>2.04</v>
+        <v>2.79</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>2.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.16</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="AC6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA6" t="n">
         <v>1.67</v>
       </c>
-      <c r="AD6" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
       <c r="BB6" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.04</v>
+        <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.53</v>
+        <v>3.86</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,80 +2180,80 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="S9" t="n">
-        <v>2.44</v>
+        <v>3.1</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>5.94</v>
+        <v>4.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X9" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.45</v>
+        <v>2.35</v>
       </c>
       <c r="AE9" t="n">
         <v>2.5</v>
       </c>
       <c r="AF9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN9" t="n">
         <v>1.48</v>
       </c>
-      <c r="AG9" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BC9" t="n">
-        <v>2.56</v>
+        <v>2.67</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>2.44</v>
       </c>
       <c r="T10" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U10" t="n">
-        <v>4.25</v>
+        <v>5.94</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X10" t="n">
-        <v>3.58</v>
+        <v>3.42</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="AE10" t="n">
         <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AI10" t="n">
-        <v>12</v>
+        <v>9.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.11</v>
+        <v>2.22</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.48</v>
+        <v>1.87</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.67</v>
+        <v>2.56</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,34 +2574,34 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="n">
         <v>2.8</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.7</v>
-      </c>
       <c r="S11" t="n">
-        <v>3.48</v>
+        <v>3.52</v>
       </c>
       <c r="T11" t="n">
         <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="V11" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="X11" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="Z11" t="n">
         <v>11.5</v>
@@ -2610,7 +2610,7 @@
         <v>1.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
         <v>1.61</v>
@@ -2619,31 +2619,31 @@
         <v>2.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="AF11" t="n">
         <v>1.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.65</v>
+        <v>6.15</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AN11" t="n">
         <v>1.37</v>
@@ -2688,16 +2688,16 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BF11" t="n">
         <v>1.04</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,34 +2771,34 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="S12" t="n">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="T12" t="n">
         <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="W12" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="X12" t="n">
-        <v>4.1</v>
+        <v>3.92</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
         <v>11.5</v>
@@ -2807,7 +2807,7 @@
         <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="AC12" t="n">
         <v>1.61</v>
@@ -2816,31 +2816,31 @@
         <v>2.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
         <v>1.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.15</v>
+        <v>5.65</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AN12" t="n">
         <v>1.37</v>
@@ -2885,16 +2885,16 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.97</v>
+        <v>2.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF12" t="n">
         <v>1.04</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="S14" t="n">
-        <v>3.67</v>
+        <v>2.85</v>
       </c>
       <c r="T14" t="n">
-        <v>2.2</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>3.01</v>
+        <v>4.68</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="W14" t="n">
-        <v>2.73</v>
+        <v>2.24</v>
       </c>
       <c r="X14" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB14" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="BC14" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF14" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>2.85</v>
+        <v>3.67</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>4.68</v>
+        <v>3.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.73</v>
       </c>
       <c r="X15" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="Y15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z15" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2.67</v>
+        <v>2.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.38</v>
+        <v>1.65</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="U16" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="W16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD16" t="n">
         <v>3.3</v>
       </c>
-      <c r="X16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.55</v>
-      </c>
       <c r="BE16" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.36</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>1.81</v>
       </c>
       <c r="S17" t="n">
-        <v>1.78</v>
+        <v>4</v>
       </c>
       <c r="T17" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
         <v>2.56</v>
       </c>
-      <c r="U17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="V17" t="n">
+      <c r="AH17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.19</v>
       </c>
-      <c r="W17" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.89</v>
+        <v>1.22</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.27</v>
+        <v>1.58</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.44</v>
+        <v>2.27</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.71</v>
+        <v>2.55</v>
       </c>
       <c r="AT17" t="n">
-        <v>2.1</v>
+        <v>3.33</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.3</v>
+        <v>2.23</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.5</v>
+        <v>1.77</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.98</v>
+        <v>1.45</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.29</v>
+        <v>2.38</v>
       </c>
       <c r="BA17" t="n">
-        <v>4</v>
+        <v>1.76</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.8</v>
+        <v>4.55</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>4.53</v>
+        <v>1.37</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="R18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.67</v>
       </c>
-      <c r="S18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W18" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z18" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AD18" t="n">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.66</v>
+        <v>1.37</v>
       </c>
       <c r="AF18" t="n">
-        <v>2</v>
+        <v>2.66</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.7</v>
+        <v>3.2</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.13</v>
+        <v>1.26</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.68</v>
+        <v>1.11</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.17</v>
+        <v>2.89</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.37</v>
+        <v>1.05</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.7</v>
+        <v>1.19</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.54</v>
+        <v>1.4</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.83</v>
+        <v>1.69</v>
       </c>
       <c r="AT18" t="n">
-        <v>4.03</v>
+        <v>2.08</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.71</v>
+        <v>5.87</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.03</v>
+        <v>3.73</v>
       </c>
       <c r="AW18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY18" t="n">
         <v>1.62</v>
       </c>
-      <c r="AX18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.16</v>
-      </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.3</v>
+        <v>5.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.699999999999999</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>13</v>
+        <v>3.49</v>
       </c>
       <c r="S20" t="n">
-        <v>1.36</v>
+        <v>2.8</v>
       </c>
       <c r="T20" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="U20" t="n">
-        <v>10</v>
+        <v>4.82</v>
       </c>
       <c r="V20" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="X20" t="n">
-        <v>1.69</v>
+        <v>3.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.05</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.28</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>1</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AK20" t="n">
-        <v>1.79</v>
+        <v>2.14</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.06</v>
+        <v>1.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>5.75</v>
+        <v>1.62</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.38</v>
+        <v>2.62</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>2.88</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.81</v>
+        <v>1.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.6</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R21" t="n">
-        <v>3.49</v>
+        <v>13</v>
       </c>
       <c r="S21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AV21" t="n">
         <v>2.8</v>
       </c>
-      <c r="T21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.62</v>
+        <v>1.38</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.88</v>
+        <v>7.8</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.4</v>
+        <v>2.81</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.09</v>
+        <v>1.6</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,79 +4741,79 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="U22" t="n">
-        <v>6.5</v>
+        <v>5.3</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>2.95</v>
+        <v>2.55</v>
       </c>
       <c r="X22" t="n">
-        <v>2.4</v>
+        <v>3.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.1</v>
+        <v>6.65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.64</v>
+        <v>1.96</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
@@ -4855,19 +4855,19 @@
         <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.93</v>
+        <v>2.22</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S23" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="T23" t="n">
-        <v>2.04</v>
+        <v>2.38</v>
       </c>
       <c r="U23" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="V23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.36</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X23" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AI23" t="n">
-        <v>6.65</v>
+        <v>5.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.96</v>
+        <v>2.64</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5923,19 +5923,19 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="R28" t="n">
         <v>3.5</v>
       </c>
       <c r="S28" t="n">
-        <v>2.54</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>2.03</v>
+        <v>2.2</v>
       </c>
       <c r="U28" t="n">
         <v>4</v>
@@ -5977,7 +5977,7 @@
         <v>3.45</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AI28" t="n">
         <v>6.25</v>
@@ -5995,40 +5995,40 @@
         <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ28" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,13 +801,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="R2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
         <v>2.64</v>
@@ -843,43 +843,43 @@
         <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AG2" t="n">
         <v>3.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="AL2" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AM2" t="n">
         <v>1.24</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.59</v>
+        <v>1.54</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.64</v>
@@ -888,25 +888,25 @@
         <v>2.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="AV2" t="n">
         <v>2.12</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.71</v>
@@ -921,7 +921,7 @@
         <v>2.06</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="BE2" t="n">
         <v>1.66</v>
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.11</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>2.32</v>
       </c>
       <c r="R3" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="S3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="n">
-        <v>3.36</v>
+        <v>3.62</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.98</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
-        <v>4.15</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="Z3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>6.25</v>
+        <v>8.1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AI3" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AJ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF3" t="n">
         <v>1.02</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,28 +1195,28 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="R4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S4" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.29</v>
       </c>
       <c r="U4" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W4" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="X4" t="n">
         <v>2.18</v>
@@ -1225,7 +1225,7 @@
         <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="AA4" t="n">
         <v>1.12</v>
@@ -1237,37 +1237,37 @@
         <v>1.11</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AE4" t="n">
         <v>1.5</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AG4" t="n">
         <v>2.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.68</v>
+        <v>3.58</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,25 +1279,25 @@
         <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.27</v>
+        <v>1.96</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.48</v>
+        <v>3.5</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AW4" t="n">
         <v>1.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AY4" t="n">
         <v>1.22</v>
@@ -1315,7 +1315,7 @@
         <v>1.69</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BE4" t="n">
         <v>2.04</v>
@@ -1392,58 +1392,58 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="R5" t="n">
-        <v>3.02</v>
+        <v>3.47</v>
       </c>
       <c r="S5" t="n">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="T5" t="n">
         <v>1.7</v>
       </c>
       <c r="U5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
         <v>1.68</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="X5" t="n">
         <v>4.2</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB5" t="n">
         <v>1.1</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AD5" t="n">
         <v>2.07</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.12</v>
+        <v>3.04</v>
       </c>
       <c r="AF5" t="n">
         <v>1.29</v>
       </c>
       <c r="AG5" t="n">
-        <v>4.7</v>
+        <v>6.5</v>
       </c>
       <c r="AH5" t="n">
         <v>1.05</v>
@@ -1455,49 +1455,49 @@
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="AM5" t="n">
         <v>1.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
@@ -1509,16 +1509,16 @@
         <v>1.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="BD5" t="n">
         <v>2.53</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>5.18</v>
+        <v>4.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R6" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1604,7 +1604,7 @@
         <v>2.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
@@ -1616,40 +1616,40 @@
         <v>2.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AA6" t="n">
         <v>1.04</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.34</v>
+        <v>3</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.16</v>
+        <v>3.35</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AI6" t="n">
-        <v>6.1</v>
+        <v>6.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="AK6" t="n">
         <v>1.8</v>
@@ -1658,10 +1658,10 @@
         <v>1.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
@@ -1703,13 +1703,13 @@
         <v>1.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC6" t="n">
         <v>2.05</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="BE6" t="n">
         <v>1.67</v>
@@ -1792,13 +1792,13 @@
         <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S7" t="n">
-        <v>4.14</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
         <v>3.32</v>
@@ -1810,7 +1810,7 @@
         <v>2.11</v>
       </c>
       <c r="X7" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="Y7" t="n">
         <v>1.19</v>
@@ -1825,19 +1825,19 @@
         <v>1.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.45</v>
+        <v>2.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="AH7" t="n">
         <v>1.09</v>
@@ -1846,10 +1846,10 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AL7" t="n">
         <v>1.57</v>
@@ -1864,34 +1864,34 @@
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -1900,13 +1900,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.83</v>
+        <v>2.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="BE7" t="n">
         <v>1.34</v>
@@ -1983,79 +1983,79 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>4.46</v>
+        <v>4.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="S8" t="n">
-        <v>5.59</v>
+        <v>5.71</v>
       </c>
       <c r="T8" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W8" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>3</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AB8" t="n">
         <v>1.06</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="AD8" t="n">
         <v>2.83</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.76</v>
+        <v>3.84</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL8" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AM8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -2097,16 +2097,16 @@
         <v>0</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BC8" t="n">
         <v>2.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="BF8" t="n">
         <v>1.13</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>2.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="R9" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U9" t="n">
-        <v>4.25</v>
+        <v>3.76</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W9" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="X9" t="n">
-        <v>3.58</v>
+        <v>3.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.35</v>
+        <v>2.27</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.5</v>
+        <v>2.95</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AG9" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="AI9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ9" t="n">
         <v>1.03</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.35</v>
       </c>
-      <c r="BC9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.38</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,22 +2377,22 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>4.75</v>
+        <v>5.36</v>
       </c>
       <c r="S10" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="T10" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="U10" t="n">
-        <v>5.94</v>
+        <v>6.54</v>
       </c>
       <c r="V10" t="n">
         <v>1.55</v>
@@ -2413,43 +2413,43 @@
         <v>1.01</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>2.42</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AG10" t="n">
         <v>4.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AI10" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.6</v>
+        <v>2.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="R11" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="S11" t="n">
-        <v>3.52</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U11" t="n">
-        <v>3.74</v>
+        <v>3.85</v>
       </c>
       <c r="V11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W11" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AL11" t="n">
         <v>1.63</v>
       </c>
-      <c r="W11" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="X11" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AM11" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BE11" t="n">
         <v>1.39</v>
       </c>
-      <c r="BC11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.31</v>
-      </c>
       <c r="BF11" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2771,22 +2771,22 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R12" t="n">
         <v>2.7</v>
       </c>
       <c r="S12" t="n">
-        <v>3.48</v>
+        <v>3.27</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>3.78</v>
+        <v>4.24</v>
       </c>
       <c r="V12" t="n">
         <v>1.64</v>
@@ -2795,55 +2795,55 @@
         <v>2.1</v>
       </c>
       <c r="X12" t="n">
-        <v>3.92</v>
+        <v>3.94</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="Z12" t="n">
         <v>11.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AI12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,16 +2885,16 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BF12" t="n">
         <v>1.04</v>
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,112 +2968,112 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>3.06</v>
       </c>
       <c r="R13" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="S13" t="n">
-        <v>3.54</v>
+        <v>3.69</v>
       </c>
       <c r="T13" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="U13" t="n">
-        <v>4.11</v>
+        <v>3.01</v>
       </c>
       <c r="V13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK13" t="n">
         <v>1.63</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="X13" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AL13" t="n">
-        <v>1.55</v>
+        <v>1.98</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AN13" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>5.94</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.9</v>
+        <v>2.11</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3165,113 +3165,113 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.85</v>
+        <v>2.97</v>
       </c>
       <c r="T14" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="U14" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="V14" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="W14" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="X14" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Z14" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AA14" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB14" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ14" t="n">
+      <c r="AK14" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AY14" t="n">
         <v>1.03</v>
       </c>
-      <c r="AK14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="BD14" t="n">
         <v>2.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R15" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R15" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S15" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="U15" t="n">
-        <v>3.01</v>
+        <v>3.5</v>
       </c>
       <c r="V15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.4</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA15" t="n">
+      <c r="BC15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.18</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>4.53</v>
+        <v>3.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="T16" t="n">
-        <v>2.12</v>
+        <v>2.27</v>
       </c>
       <c r="U16" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="V16" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="W16" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="X16" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK16" t="n">
+      <c r="AQ16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC16" t="n">
         <v>1.85</v>
       </c>
-      <c r="AL16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
+      <c r="BD16" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.29</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>4.53</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="R17" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
       <c r="U17" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="W17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD17" t="n">
         <v>3.3</v>
       </c>
-      <c r="X17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.55</v>
-      </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>1.57</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.21</v>
+        <v>1.14</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -4150,130 +4150,130 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>8.15</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="T19" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="U19" t="n">
-        <v>6.3</v>
+        <v>5.75</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W19" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="X19" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="AE19" t="n">
         <v>1.7</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AL19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.81</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.8</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>9.75</v>
       </c>
       <c r="R20" t="n">
-        <v>3.49</v>
+        <v>13.07</v>
       </c>
       <c r="S20" t="n">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1.85</v>
+        <v>3.35</v>
       </c>
       <c r="U20" t="n">
-        <v>4.82</v>
+        <v>10</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="W20" t="n">
-        <v>2.24</v>
+        <v>5</v>
       </c>
       <c r="X20" t="n">
-        <v>3.5</v>
+        <v>1.69</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>2.04</v>
       </c>
       <c r="Z20" t="n">
-        <v>8.800000000000001</v>
+        <v>3.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>1.28</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.39</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.6</v>
+        <v>1.19</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.44</v>
+        <v>4.05</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.75</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.12</v>
+        <v>2.35</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.300000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>1.64</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.62</v>
+        <v>7.2</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>8.9</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.88</v>
+        <v>7</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.4</v>
+        <v>2.84</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R21" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q21" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="R21" t="n">
-        <v>13</v>
-      </c>
-      <c r="S21" t="n">
+      <c r="AI21" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.36</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U21" t="n">
-        <v>10</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W21" t="n">
-        <v>5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AE21" t="n">
+      <c r="AQ21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AY21" t="n">
         <v>1.17</v>
       </c>
-      <c r="AF21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.35</v>
       </c>
-      <c r="AR21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AV21" t="n">
+      <c r="BC21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BD21" t="n">
         <v>2.8</v>
       </c>
-      <c r="AW21" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE21" t="n">
-        <v>2.81</v>
+        <v>1.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S22" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="T22" t="n">
-        <v>2.04</v>
+        <v>2.52</v>
       </c>
       <c r="U22" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="V22" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH22" t="n">
         <v>1.36</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AF22" t="n">
+      <c r="AI22" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AQ22" t="n">
         <v>1.72</v>
       </c>
-      <c r="AG22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC22" t="n">
-        <v>2.22</v>
+        <v>1.93</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="R23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S23" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T23" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="U23" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="V23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.32</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z23" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.68</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AJ23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AY23" t="n">
         <v>1.11</v>
       </c>
-      <c r="AK23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5150,49 +5150,49 @@
         <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V24" t="n">
         <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="Z24" t="n">
         <v>6.3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AB24" t="n">
         <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
         <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="AG24" t="n">
-        <v>3.15</v>
+        <v>2.92</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.47</v>
+        <v>5.5</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.08</v>
@@ -5204,34 +5204,34 @@
         <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AS24" t="n">
         <v>2.26</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.55</v>
+        <v>2.98</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.7</v>
+        <v>3.39</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="AW24" t="n">
         <v>1.94</v>
@@ -5255,10 +5255,10 @@
         <v>2</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="BF24" t="n">
         <v>1.16</v>
@@ -5332,34 +5332,34 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>5.25</v>
+        <v>4.85</v>
       </c>
       <c r="S25" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="T25" t="n">
         <v>1.97</v>
       </c>
       <c r="U25" t="n">
-        <v>6.91</v>
+        <v>6.85</v>
       </c>
       <c r="V25" t="n">
         <v>1.48</v>
       </c>
       <c r="W25" t="n">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="X25" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="Z25" t="n">
         <v>8.1</v>
@@ -5368,10 +5368,10 @@
         <v>1.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="AD25" t="n">
         <v>2.62</v>
@@ -5398,46 +5398,46 @@
         <v>2.28</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
         <v>0</v>
@@ -5455,7 +5455,7 @@
         <v>3.18</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF25" t="n">
         <v>1.1</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.41</v>
+        <v>2.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.63</v>
+        <v>2.83</v>
       </c>
       <c r="R26" t="n">
-        <v>1.62</v>
+        <v>3.33</v>
       </c>
       <c r="S26" t="n">
         <v>5.46</v>
@@ -5577,7 +5577,7 @@
         <v>2.1</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AG26" t="n">
         <v>3.08</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -801,10 +801,10 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
         <v>3</v>
@@ -816,7 +816,7 @@
         <v>2.15</v>
       </c>
       <c r="U2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.34</v>
@@ -837,49 +837,49 @@
         <v>1.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC2" t="n">
         <v>1.28</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.28</v>
+        <v>2.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.86</v>
+        <v>2.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AG2" t="n">
         <v>3.2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>5.75</v>
+        <v>7.3</v>
       </c>
       <c r="AJ2" t="n">
         <v>1.12</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="AL2" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="AO2" t="n">
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.64</v>
@@ -891,10 +891,10 @@
         <v>2.68</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="AV2" t="n">
         <v>2.12</v>
@@ -906,7 +906,7 @@
         <v>1.38</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AZ2" t="n">
         <v>1.71</v>
@@ -915,19 +915,19 @@
         <v>2.72</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.06</v>
+        <v>2.29</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="BG2" t="n">
         <v>0</v>
@@ -1001,82 +1001,82 @@
         <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="U3" t="n">
-        <v>3.62</v>
+        <v>3.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="AE3" t="n">
-        <v>3</v>
+        <v>3.42</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AG3" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.01</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AQ3" t="n">
         <v>2.21</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>2.55</v>
+        <v>4.78</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.63</v>
+        <v>3.54</v>
       </c>
       <c r="R5" t="n">
-        <v>3.47</v>
+        <v>1.6</v>
       </c>
       <c r="S5" t="n">
-        <v>3.22</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>2.22</v>
       </c>
       <c r="V5" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="W5" t="n">
-        <v>2.03</v>
+        <v>2.79</v>
       </c>
       <c r="X5" t="n">
-        <v>4.2</v>
+        <v>2.85</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.42</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BE5" t="n">
         <v>1.66</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BF5" t="n">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1589,133 +1589,133 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>4.65</v>
+        <v>2.55</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.7</v>
+        <v>2.63</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>3.47</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3.24</v>
       </c>
       <c r="T6" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>2.19</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="W6" t="n">
-        <v>2.79</v>
+        <v>2.06</v>
       </c>
       <c r="X6" t="n">
-        <v>2.73</v>
+        <v>4.2</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z6" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC6" t="n">
-        <v>2.05</v>
+        <v>3.08</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.88</v>
+        <v>2.53</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.67</v>
+        <v>1.29</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1792,13 +1792,13 @@
         <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="S7" t="n">
         <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="U7" t="n">
         <v>3.32</v>
@@ -1855,16 +1855,16 @@
         <v>1.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.21</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,79 +2180,79 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
       <c r="R9" t="n">
-        <v>2.76</v>
+        <v>3.12</v>
       </c>
       <c r="S9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X9" t="n">
         <v>3.5</v>
       </c>
-      <c r="T9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X9" t="n">
-        <v>3.88</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AA9" t="n">
         <v>1.04</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.95</v>
+        <v>2.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.16</v>
+        <v>2.09</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BC9" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BD9" t="n">
         <v>2.79</v>
       </c>
-      <c r="BD9" t="n">
-        <v>2.75</v>
-      </c>
       <c r="BE9" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,133 +2574,133 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.51</v>
+        <v>2.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.69</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
-        <v>3.12</v>
+        <v>2.76</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T11" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.85</v>
+        <v>3.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="X11" t="n">
-        <v>3.5</v>
+        <v>3.88</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.62</v>
+        <v>2.95</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF11" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>2.97</v>
       </c>
       <c r="T14" t="n">
-        <v>1.77</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
         <v>4.74</v>
@@ -3246,7 +3246,7 @@
         <v>1.66</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AR14" t="n">
         <v>3.74</v>
@@ -3261,7 +3261,7 @@
         <v>2.08</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AW14" t="n">
         <v>1.34</v>
@@ -3282,7 +3282,7 @@
         <v>1.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="BD14" t="n">
         <v>2.75</v>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>3.9</v>
+        <v>4.53</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="R16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.79</v>
       </c>
-      <c r="S16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE16" t="n">
+      <c r="AN16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AW16" t="n">
         <v>1.62</v>
       </c>
-      <c r="AF16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AX16" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.26</v>
+        <v>1.16</v>
       </c>
       <c r="AZ16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.14</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.55</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.29</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>4.53</v>
+        <v>1.37</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.67</v>
       </c>
-      <c r="S17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
       <c r="Z17" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.07</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.02</v>
+        <v>2.66</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.22</v>
+        <v>1.71</v>
       </c>
       <c r="AI17" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="AJ17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.08</v>
       </c>
-      <c r="AK17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>4.03</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BC17" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.3</v>
+        <v>5.65</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.14</v>
+        <v>1.35</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5.75</v>
+        <v>1.79</v>
       </c>
       <c r="S18" t="n">
-        <v>1.78</v>
+        <v>4.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>5.8</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.19</v>
       </c>
-      <c r="W18" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.14</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ18" t="n">
+      <c r="BC18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.29</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.35</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.82</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AH20" t="n">
         <v>1.11</v>
       </c>
-      <c r="Q20" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>13.07</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="AI20" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
         <v>1.36</v>
       </c>
-      <c r="T20" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W20" t="n">
-        <v>5</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AQ20" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.96</v>
+        <v>2.77</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.48</v>
+        <v>3.91</v>
       </c>
       <c r="AU20" t="n">
-        <v>4.1</v>
+        <v>2.77</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.98</v>
+        <v>2.07</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.08</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.65</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>1.11</v>
       </c>
       <c r="Q21" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV21" t="n">
         <v>2.98</v>
       </c>
-      <c r="R21" t="n">
-        <v>3.49</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.07</v>
-      </c>
       <c r="AW21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.08</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Dijon</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="R22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S22" t="n">
-        <v>1.91</v>
+        <v>2.33</v>
       </c>
       <c r="T22" t="n">
-        <v>2.52</v>
+        <v>2.14</v>
       </c>
       <c r="U22" t="n">
-        <v>6.5</v>
+        <v>4.6</v>
       </c>
       <c r="V22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y22" t="n">
         <v>1.32</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.44</v>
-      </c>
       <c r="Z22" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.7</v>
+        <v>3.09</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.72</v>
+        <v>2.13</v>
       </c>
       <c r="AF22" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.85</v>
+        <v>6.8</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="AL22" t="n">
         <v>1.77</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.75</v>
+        <v>1.89</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.17</v>
+        <v>2.31</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.32</v>
+        <v>1.54</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.56</v>
+        <v>2.88</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.93</v>
+        <v>2.26</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.05</v>
+        <v>3.34</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.19</v>
+        <v>1.11</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Dijon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S23" t="n">
-        <v>2.33</v>
+        <v>1.91</v>
       </c>
       <c r="T23" t="n">
-        <v>2.14</v>
+        <v>2.52</v>
       </c>
       <c r="U23" t="n">
-        <v>4.6</v>
+        <v>6.5</v>
       </c>
       <c r="V23" t="n">
-        <v>1.42</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>2.56</v>
+        <v>2.96</v>
       </c>
       <c r="X23" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AC23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD23" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AI23" t="n">
-        <v>6.8</v>
+        <v>4.85</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="AL23" t="n">
         <v>1.77</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.89</v>
+        <v>2.75</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.31</v>
+        <v>2.17</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.6</v>
+        <v>4.35</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.88</v>
+        <v>5.56</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.24</v>
+        <v>1.17</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.34</v>
+        <v>4.05</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.56</v>
+        <v>1.77</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
         <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
         <v>3.9</v>
@@ -5771,10 +5771,10 @@
         <v>2.1</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AG27" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -775,13 +775,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -790,14 +790,14 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -1589,13 +1589,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="R6" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="S6" t="n">
         <v>3.24</v>
@@ -1604,13 +1604,13 @@
         <v>1.69</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="V6" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W6" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="X6" t="n">
         <v>4.2</v>
@@ -1631,13 +1631,13 @@
         <v>1.65</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AE6" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AG6" t="n">
         <v>6.45</v>
@@ -1792,25 +1792,25 @@
         <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S7" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.97</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.32</v>
+        <v>3.34</v>
       </c>
       <c r="V7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="W7" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="X7" t="n">
-        <v>3.78</v>
+        <v>3.8</v>
       </c>
       <c r="Y7" t="n">
         <v>1.19</v>
@@ -1855,16 +1855,16 @@
         <v>1.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AQ7" t="n">
         <v>2.21</v>
@@ -1879,7 +1879,7 @@
         <v>7.1</v>
       </c>
       <c r="AU7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AV7" t="n">
         <v>1.58</v>
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.51</v>
+        <v>2.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>3.12</v>
+        <v>2.7</v>
       </c>
       <c r="S9" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="U9" t="n">
-        <v>3.85</v>
+        <v>4.24</v>
       </c>
       <c r="V9" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF9" t="n">
         <v>1.04</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>12</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>2.51</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>2.69</v>
       </c>
       <c r="R10" t="n">
-        <v>5.36</v>
+        <v>3.12</v>
       </c>
       <c r="S10" t="n">
-        <v>2.32</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="U10" t="n">
-        <v>6.54</v>
+        <v>3.85</v>
       </c>
       <c r="V10" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W10" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="X10" t="n">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="Z10" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AC10" t="n">
         <v>1.48</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.29</v>
+        <v>2.09</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.83</v>
+        <v>1.48</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.88</v>
+        <v>2.79</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>2.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="R11" t="n">
-        <v>2.76</v>
+        <v>5.36</v>
       </c>
       <c r="S11" t="n">
-        <v>3.5</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="U11" t="n">
-        <v>3.76</v>
+        <v>6.54</v>
       </c>
       <c r="V11" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="W11" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>3.88</v>
+        <v>3.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.95</v>
+        <v>2.42</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.79</v>
+        <v>2.56</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="S12" t="n">
-        <v>3.27</v>
+        <v>3.5</v>
       </c>
       <c r="T12" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>4.24</v>
+        <v>3.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="W12" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="X12" t="n">
-        <v>3.94</v>
+        <v>3.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
         <v>11.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.13</v>
+        <v>2.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.83</v>
+        <v>2.95</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.27</v>
+        <v>2.16</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="AM12" t="n">
         <v>1.34</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,16 +2885,16 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.56</v>
+        <v>2.75</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="BF12" t="n">
         <v>1.04</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.06</v>
+        <v>2.85</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="S13" t="n">
-        <v>3.69</v>
+        <v>2.9</v>
       </c>
       <c r="T13" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="U13" t="n">
-        <v>3.01</v>
+        <v>4.96</v>
       </c>
       <c r="V13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
         <v>1.41</v>
       </c>
-      <c r="W13" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="AJ13" t="n">
+      <c r="BC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF13" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3117,7 +3117,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Difaâ El Jadida</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>CR Khemis Zemamra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R14" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="S14" t="n">
-        <v>2.97</v>
+        <v>3.84</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>4.74</v>
+        <v>3.39</v>
       </c>
       <c r="V14" t="n">
-        <v>1.63</v>
+        <v>1.52</v>
       </c>
       <c r="W14" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="X14" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="n">
         <v>1.01</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>5.45</v>
+        <v>4.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AI14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.27</v>
+        <v>2.23</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>1.66</v>
       </c>
       <c r="AQ14" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AR14" t="n">
         <v>3.74</v>
@@ -3261,7 +3261,7 @@
         <v>2.08</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AW14" t="n">
         <v>1.34</v>
@@ -3282,13 +3282,13 @@
         <v>1.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="BD14" t="n">
         <v>2.75</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.33</v>
+        <v>1.42</v>
       </c>
       <c r="BF14" t="n">
         <v>1.06</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Difaâ El Jadida</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CR Khemis Zemamra</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,112 +3362,112 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="S15" t="n">
-        <v>3.29</v>
+        <v>3.79</v>
       </c>
       <c r="T15" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="V15" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>2.1</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
-        <v>4</v>
+        <v>2.82</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="Z15" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.15</v>
+        <v>3.08</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.89</v>
+        <v>1.84</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.5</v>
+        <v>3.2</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.07</v>
+        <v>1.26</v>
       </c>
       <c r="AI15" t="n">
-        <v>10.5</v>
+        <v>6.15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.23</v>
+        <v>1.63</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.57</v>
+        <v>1.97</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AR15" t="n">
-        <v>3.74</v>
+        <v>3.48</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.13</v>
+        <v>3.85</v>
       </c>
       <c r="AT15" t="n">
-        <v>6.49</v>
+        <v>5.94</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -3476,19 +3476,19 @@
         <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.9</v>
+        <v>2.13</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>5.75</v>
+        <v>1.79</v>
       </c>
       <c r="S17" t="n">
-        <v>1.78</v>
+        <v>4.25</v>
       </c>
       <c r="T17" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="U17" t="n">
-        <v>5.8</v>
+        <v>2.27</v>
       </c>
       <c r="V17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
         <v>1.19</v>
       </c>
-      <c r="W17" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB17" t="n">
         <v>1.14</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ17" t="n">
+      <c r="BC17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF17" t="n">
         <v>1.29</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.35</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.9</v>
+        <v>1.37</v>
       </c>
       <c r="Q18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA18" t="n">
         <v>4</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="BB18" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ18" t="n">
+      <c r="BC18" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR18" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD18" t="n">
-        <v>4.55</v>
+        <v>5.65</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4347,31 +4347,31 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
         <v>2.98</v>
       </c>
       <c r="R20" t="n">
-        <v>3.49</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="T20" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="U20" t="n">
-        <v>4.82</v>
+        <v>4.33</v>
       </c>
       <c r="V20" t="n">
         <v>1.5</v>
       </c>
       <c r="W20" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="X20" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="Y20" t="n">
         <v>1.25</v>
@@ -4380,31 +4380,31 @@
         <v>11</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AC20" t="n">
         <v>1.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="AE20" t="n">
         <v>2.6</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AG20" t="n">
-        <v>4.8</v>
+        <v>4.95</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AI20" t="n">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ20" t="n">
         <v>1</v>
@@ -4416,10 +4416,10 @@
         <v>1.62</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,16 +4461,16 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF20" t="n">
         <v>1.08</v>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q25" t="n">
         <v>3.4</v>
@@ -5341,55 +5341,55 @@
         <v>4.85</v>
       </c>
       <c r="S25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="T25" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="U25" t="n">
-        <v>6.85</v>
+        <v>6.91</v>
       </c>
       <c r="V25" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="X25" t="n">
         <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Z25" t="n">
         <v>8.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB25" t="n">
         <v>1.04</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AG25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AI25" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AJ25" t="n">
         <v>1</v>
@@ -5398,7 +5398,7 @@
         <v>2.28</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="AM25" t="n">
         <v>1.23</v>
@@ -5446,16 +5446,16 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BC25" t="n">
         <v>2.3</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="BF25" t="n">
         <v>1.1</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -981,20 +981,20 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1166,108 +1166,108 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S4" t="n">
-        <v>3.26</v>
+        <v>3.06</v>
       </c>
       <c r="T4" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
         <v>2.75</v>
       </c>
       <c r="V4" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>3.42</v>
+        <v>3.8</v>
       </c>
       <c r="X4" t="n">
-        <v>2.18</v>
+        <v>2.02</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.95</v>
+        <v>5.75</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="AI4" t="n">
-        <v>3.58</v>
+        <v>3.08</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.66</v>
+        <v>2.95</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1279,25 +1279,25 @@
         <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.96</v>
+        <v>2.27</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="AU4" t="n">
         <v>3.05</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="AW4" t="n">
         <v>1.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AY4" t="n">
         <v>1.22</v>
@@ -1306,22 +1306,22 @@
         <v>1.97</v>
       </c>
       <c r="BA4" t="n">
-        <v>2.35</v>
+        <v>2.22</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.1</v>
+        <v>6.1</v>
       </c>
       <c r="BE4" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bhayangkara</t>
+          <t>Negele Arsi Ketema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Persib</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1381,144 +1381,144 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>4.78</v>
+        <v>2.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.54</v>
+        <v>2.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6</v>
+        <v>3.25</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>3.24</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="U5" t="n">
-        <v>2.22</v>
+        <v>4.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.35</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>2.79</v>
+        <v>2.02</v>
       </c>
       <c r="X5" t="n">
-        <v>2.85</v>
+        <v>4.2</v>
       </c>
       <c r="Y5" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.42</v>
       </c>
-      <c r="Z5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.06</v>
+        <v>3.08</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.86</v>
+        <v>2.53</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.14</v>
+        <v>1.06</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,171 +1551,171 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Negele Arsi Ketema</t>
+          <t>Bhayangkara</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Persib</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>4.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.62</v>
+        <v>3.4</v>
       </c>
       <c r="R6" t="n">
-        <v>3.25</v>
+        <v>1.6</v>
       </c>
       <c r="S6" t="n">
-        <v>3.24</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="U6" t="n">
-        <v>4.8</v>
+        <v>2.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.69</v>
+        <v>1.37</v>
       </c>
       <c r="W6" t="n">
-        <v>2.02</v>
+        <v>2.71</v>
       </c>
       <c r="X6" t="n">
-        <v>4.2</v>
+        <v>2.96</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>7.3</v>
       </c>
       <c r="AA6" t="n">
         <v>1.03</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.08</v>
+        <v>3.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>1.97</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>6.45</v>
+        <v>3.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="AI6" t="n">
-        <v>17</v>
+        <v>6.25</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK6" t="n">
-        <v>2.36</v>
+        <v>1.8</v>
       </c>
       <c r="AL6" t="n">
-        <v>1.5</v>
+        <v>1.84</v>
       </c>
       <c r="AM6" t="n">
-        <v>1.38</v>
+        <v>1.21</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.48</v>
+        <v>1.11</v>
       </c>
       <c r="AO6" t="n">
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.5</v>
+        <v>1.46</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.05</v>
+        <v>1.96</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.51</v>
+        <v>2.19</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.1</v>
+        <v>2.89</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.81</v>
+        <v>3.64</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.44</v>
+        <v>2.54</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.21</v>
+        <v>1.96</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.06</v>
+        <v>1.59</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.08</v>
+        <v>2.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>2.53</v>
+        <v>3.78</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="BG6" t="n">
         <v>0</v>
@@ -1775,14 +1775,14 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Ben Guerdane</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,67 +2180,67 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>2.6</v>
+        <v>2.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7</v>
+        <v>3.07</v>
       </c>
       <c r="S9" t="n">
-        <v>3.27</v>
+        <v>2.94</v>
       </c>
       <c r="T9" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="U9" t="n">
-        <v>4.24</v>
+        <v>4.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="X9" t="n">
-        <v>3.94</v>
+        <v>3.98</v>
       </c>
       <c r="Y9" t="n">
         <v>1.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>5.75</v>
+        <v>6.05</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AK9" t="n">
         <v>2.27</v>
@@ -2249,10 +2249,10 @@
         <v>1.54</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2294,19 +2294,19 @@
         <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BC9" t="n">
         <v>2.92</v>
       </c>
       <c r="BD9" t="n">
-        <v>2.56</v>
+        <v>2.71</v>
       </c>
       <c r="BE9" t="n">
         <v>1.32</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2377,79 +2377,79 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>2.51</v>
+        <v>2.05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="U10" t="n">
-        <v>3.85</v>
+        <v>4.25</v>
       </c>
       <c r="V10" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W10" t="n">
-        <v>2.22</v>
+        <v>2.31</v>
       </c>
       <c r="X10" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="Z10" t="n">
         <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AB10" t="n">
         <v>1.09</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.36</v>
+        <v>2.29</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="AF10" t="n">
         <v>1.42</v>
       </c>
       <c r="AG10" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AI10" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="AL10" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AM10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AO10" t="n">
         <v>0</v>
@@ -2491,19 +2491,19 @@
         <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="BD10" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2574,79 +2574,79 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>5.36</v>
+        <v>4.65</v>
       </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="T11" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="U11" t="n">
-        <v>6.54</v>
+        <v>6.1</v>
       </c>
       <c r="V11" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W11" t="n">
         <v>2.26</v>
       </c>
       <c r="X11" t="n">
-        <v>3.42</v>
+        <v>3.58</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>9.699999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.42</v>
+        <v>2.59</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AG11" t="n">
         <v>4.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AI11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AL11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
@@ -2688,19 +2688,19 @@
         <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BC11" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="BD11" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Guerdane</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,79 +2771,79 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>2.59</v>
+        <v>2.15</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R12" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="S12" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U12" t="n">
-        <v>3.76</v>
+        <v>4.74</v>
       </c>
       <c r="V12" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="W12" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="X12" t="n">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="Y12" t="n">
         <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.6</v>
+        <v>5.65</v>
       </c>
       <c r="AH12" t="n">
         <v>1.08</v>
       </c>
       <c r="AI12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
         <v>1.03</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.16</v>
+        <v>2.29</v>
       </c>
       <c r="AL12" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="AO12" t="n">
         <v>0</v>
@@ -2885,19 +2885,19 @@
         <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Olympique Dcheïra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>UTS Rabat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,133 +2968,133 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.9</v>
+        <v>3.79</v>
       </c>
       <c r="T13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.75</v>
       </c>
-      <c r="U13" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="W13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="X13" t="n">
+      <c r="AG13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="AS13" t="n">
         <v>3.85</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AT13" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AX13" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC13" t="n">
+      <c r="AY13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.63</v>
       </c>
-      <c r="AD13" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.49</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.33</v>
-      </c>
       <c r="BF13" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Olympique Dcheïra</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>UTS Rabat</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="R15" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="S15" t="n">
-        <v>3.79</v>
+        <v>2.9</v>
       </c>
       <c r="T15" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="U15" t="n">
-        <v>2.95</v>
+        <v>4.96</v>
       </c>
       <c r="V15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="X15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>6.49</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
         <v>1.41</v>
       </c>
-      <c r="W15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="BC15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.06</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>5.94</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.16</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Akhdoud</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.9</v>
+        <v>1.37</v>
       </c>
       <c r="Q17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BA17" t="n">
         <v>4</v>
       </c>
-      <c r="R17" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="S17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W17" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="BB17" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ17" t="n">
+      <c r="BC17" t="n">
         <v>1.58</v>
       </c>
-      <c r="AR17" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.85</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.55</v>
+        <v>5.65</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Al Akhdoud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.37</v>
+        <v>3.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5.75</v>
+        <v>1.79</v>
       </c>
       <c r="S18" t="n">
-        <v>1.78</v>
+        <v>4.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.56</v>
+        <v>2.27</v>
       </c>
       <c r="U18" t="n">
-        <v>5.8</v>
+        <v>2.27</v>
       </c>
       <c r="V18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.19</v>
       </c>
-      <c r="W18" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BB18" t="n">
         <v>1.14</v>
       </c>
-      <c r="AB18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.73</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AZ18" t="n">
+      <c r="BC18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.29</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.35</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco Botola Pro</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FAR Rabat</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raja Casablanca</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.11</v>
       </c>
       <c r="Q20" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W20" t="n">
+        <v>5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV20" t="n">
         <v>2.98</v>
       </c>
-      <c r="R20" t="n">
-        <v>3</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U20" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="X20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB20" t="n">
+      <c r="AW20" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.08</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AW20" t="n">
+      <c r="BC20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BF20" t="n">
         <v>1.65</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.08</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Morocco Botola Pro</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>FAR Rabat</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Raja Casablanca</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.11</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>9.75</v>
+        <v>2.98</v>
       </c>
       <c r="R21" t="n">
-        <v>13.07</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
         <v>1.36</v>
       </c>
-      <c r="T21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="U21" t="n">
-        <v>10</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W21" t="n">
-        <v>5</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.73</v>
+        <v>2.48</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.96</v>
+        <v>2.77</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.48</v>
+        <v>3.91</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.1</v>
+        <v>2.77</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.98</v>
+        <v>2.07</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.48</v>
+        <v>1.17</v>
       </c>
       <c r="AZ21" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>8.9</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.08</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.65</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>

--- a/jogos_2026-04-30.xlsx
+++ b/jogos_2026-04-30.xlsx
@@ -265,15 +265,15 @@
     <t>Morocco Botola Pro</t>
   </si>
   <si>
+    <t>Saudi Arabia Professional League</t>
+  </si>
+  <si>
+    <t>Estonia Meistriliiga</t>
+  </si>
+  <si>
     <t>Azerbaijan Premyer Liqası</t>
   </si>
   <si>
-    <t>Saudi Arabia Professional League</t>
-  </si>
-  <si>
-    <t>Estonia Meistriliiga</t>
-  </si>
-  <si>
     <t>Norway Eliteserien</t>
   </si>
   <si>
@@ -319,42 +319,42 @@
     <t>Olympique Béja</t>
   </si>
   <si>
+    <t>Marsa</t>
+  </si>
+  <si>
     <t>Kairouan</t>
   </si>
   <si>
     <t>ES Tunis</t>
   </si>
   <si>
-    <t>Marsa</t>
+    <t>Olympique Dcheïra</t>
   </si>
   <si>
     <t>Ethiopia Bunna</t>
   </si>
   <si>
-    <t>Olympique Dcheïra</t>
-  </si>
-  <si>
     <t>Difaâ El Jadida</t>
   </si>
   <si>
+    <t>Al Akhdoud</t>
+  </si>
+  <si>
+    <t>Tallinna FC Flora</t>
+  </si>
+  <si>
     <t>Neftçi</t>
   </si>
   <si>
-    <t>Al Akhdoud</t>
-  </si>
-  <si>
-    <t>Tallinna FC Flora</t>
-  </si>
-  <si>
     <t>Al Shabab</t>
   </si>
   <si>
+    <t>FK Bodo - Glimt</t>
+  </si>
+  <si>
     <t>FAR Rabat</t>
   </si>
   <si>
-    <t>FK Bodo - Glimt</t>
-  </si>
-  <si>
     <t>Dijon</t>
   </si>
   <si>
@@ -397,40 +397,40 @@
     <t>CA Bizertin</t>
   </si>
   <si>
+    <t>Zarzis</t>
+  </si>
+  <si>
     <t>Ben Guerdane</t>
   </si>
   <si>
     <t>CS Sfaxien</t>
   </si>
   <si>
-    <t>Zarzis</t>
+    <t>UTS Rabat</t>
   </si>
   <si>
     <t>Welwalo Adigrat Uni</t>
   </si>
   <si>
-    <t>UTS Rabat</t>
-  </si>
-  <si>
     <t>CR Khemis Zemamra</t>
   </si>
   <si>
+    <t>Al Ittifaq</t>
+  </si>
+  <si>
+    <t>Harju Jalgpallikool</t>
+  </si>
+  <si>
     <t>Qarabağ</t>
   </si>
   <si>
-    <t>Al Ittifaq</t>
-  </si>
-  <si>
-    <t>Harju Jalgpallikool</t>
-  </si>
-  <si>
     <t>Saham</t>
   </si>
   <si>
+    <t>Start</t>
+  </si>
+  <si>
     <t>Raja Casablanca</t>
-  </si>
-  <si>
-    <t>Start</t>
   </si>
   <si>
     <t>Châteauroux</t>
@@ -2506,16 +2506,16 @@
         <v>127</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>1</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2524,88 +2524,88 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O10" t="s">
         <v>145</v>
       </c>
       <c r="P10">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q10">
-        <v>3.1</v>
+        <v>2.88</v>
       </c>
       <c r="R10">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="S10">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="T10">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="U10">
-        <v>4.1</v>
+        <v>4.25</v>
       </c>
       <c r="V10">
+        <v>1.53</v>
+      </c>
+      <c r="W10">
+        <v>2.31</v>
+      </c>
+      <c r="X10">
+        <v>3.58</v>
+      </c>
+      <c r="Y10">
+        <v>1.21</v>
+      </c>
+      <c r="Z10">
+        <v>10.5</v>
+      </c>
+      <c r="AA10">
+        <v>1.01</v>
+      </c>
+      <c r="AB10">
+        <v>1.09</v>
+      </c>
+      <c r="AC10">
         <v>1.55</v>
       </c>
-      <c r="W10">
-        <v>2.26</v>
-      </c>
-      <c r="X10">
-        <v>3.98</v>
-      </c>
-      <c r="Y10">
-        <v>1.17</v>
-      </c>
-      <c r="Z10">
-        <v>11</v>
-      </c>
-      <c r="AA10">
-        <v>1.03</v>
-      </c>
-      <c r="AB10">
-        <v>1.13</v>
-      </c>
-      <c r="AC10">
-        <v>1.57</v>
-      </c>
       <c r="AD10">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AE10">
-        <v>2.79</v>
+        <v>2.69</v>
       </c>
       <c r="AF10">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AG10">
-        <v>6.05</v>
+        <v>4.6</v>
       </c>
       <c r="AH10">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AI10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AJ10">
         <v>1.03</v>
       </c>
       <c r="AK10">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="AL10">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AM10">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AN10">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AO10">
         <v>0</v>
@@ -2647,19 +2647,19 @@
         <v>0</v>
       </c>
       <c r="BB10">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="BC10">
-        <v>2.92</v>
+        <v>2.79</v>
       </c>
       <c r="BD10">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BE10">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="BF10">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="BG10">
         <v>0</v>
@@ -2694,13 +2694,13 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -2709,70 +2709,70 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>-1</v>
       </c>
       <c r="O11" t="s">
         <v>145</v>
       </c>
       <c r="P11">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R11">
-        <v>4.65</v>
+        <v>3.07</v>
       </c>
       <c r="S11">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="T11">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="U11">
-        <v>6.1</v>
+        <v>4.1</v>
       </c>
       <c r="V11">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="W11">
         <v>2.26</v>
       </c>
       <c r="X11">
-        <v>3.58</v>
+        <v>3.98</v>
       </c>
       <c r="Y11">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB11">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="AC11">
         <v>1.57</v>
       </c>
       <c r="AD11">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AE11">
-        <v>2.59</v>
+        <v>2.79</v>
       </c>
       <c r="AF11">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AG11">
-        <v>4.5</v>
+        <v>6.05</v>
       </c>
       <c r="AH11">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AI11">
         <v>12</v>
@@ -2781,16 +2781,16 @@
         <v>1.03</v>
       </c>
       <c r="AK11">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AL11">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="AM11">
         <v>1.28</v>
       </c>
       <c r="AN11">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AO11">
         <v>0</v>
@@ -2832,16 +2832,16 @@
         <v>0</v>
       </c>
       <c r="BB11">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BC11">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="BD11">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BE11">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="BF11">
         <v>1.05</v>
@@ -2876,13 +2876,13 @@
         <v>129</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2894,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>3</v>
@@ -2903,28 +2903,28 @@
         <v>145</v>
       </c>
       <c r="P12">
-        <v>2.05</v>
+        <v>1.75</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="R12">
-        <v>3.5</v>
+        <v>4.65</v>
       </c>
       <c r="S12">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="T12">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="U12">
-        <v>4.25</v>
+        <v>6.1</v>
       </c>
       <c r="V12">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="W12">
-        <v>2.31</v>
+        <v>2.26</v>
       </c>
       <c r="X12">
         <v>3.58</v>
@@ -2936,46 +2936,46 @@
         <v>10.5</v>
       </c>
       <c r="AA12">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AB12">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AC12">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD12">
         <v>2.29</v>
       </c>
       <c r="AE12">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="AF12">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AG12">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AH12">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AI12">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AJ12">
         <v>1.03</v>
       </c>
       <c r="AK12">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="AL12">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AM12">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AN12">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AO12">
         <v>0</v>
@@ -3017,19 +3017,19 @@
         <v>0</v>
       </c>
       <c r="BB12">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BC12">
-        <v>2.79</v>
+        <v>2.88</v>
       </c>
       <c r="BD12">
         <v>2.75</v>
       </c>
       <c r="BE12">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="BF12">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="BG12">
         <v>0</v>
@@ -3049,7 +3049,7 @@
         <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
         <v>90</v>
@@ -3061,160 +3061,160 @@
         <v>130</v>
       </c>
       <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="H13">
-        <v>4</v>
-      </c>
       <c r="I13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13">
         <v>2</v>
       </c>
       <c r="M13">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N13">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O13" t="s">
         <v>145</v>
       </c>
       <c r="P13">
-        <v>2.1</v>
+        <v>2.86</v>
       </c>
       <c r="Q13">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R13">
-        <v>3.5</v>
+        <v>2.35</v>
       </c>
       <c r="S13">
-        <v>2.9</v>
+        <v>3.79</v>
       </c>
       <c r="T13">
+        <v>2.2</v>
+      </c>
+      <c r="U13">
+        <v>2.95</v>
+      </c>
+      <c r="V13">
+        <v>1.41</v>
+      </c>
+      <c r="W13">
+        <v>2.59</v>
+      </c>
+      <c r="X13">
+        <v>2.82</v>
+      </c>
+      <c r="Y13">
+        <v>1.35</v>
+      </c>
+      <c r="Z13">
+        <v>7</v>
+      </c>
+      <c r="AA13">
+        <v>1.07</v>
+      </c>
+      <c r="AB13">
+        <v>1.02</v>
+      </c>
+      <c r="AC13">
+        <v>1.28</v>
+      </c>
+      <c r="AD13">
+        <v>3.08</v>
+      </c>
+      <c r="AE13">
+        <v>1.84</v>
+      </c>
+      <c r="AF13">
         <v>1.75</v>
       </c>
-      <c r="U13">
-        <v>4.96</v>
-      </c>
-      <c r="V13">
-        <v>1.69</v>
-      </c>
-      <c r="W13">
-        <v>2.02</v>
-      </c>
-      <c r="X13">
+      <c r="AG13">
+        <v>3.2</v>
+      </c>
+      <c r="AH13">
+        <v>1.26</v>
+      </c>
+      <c r="AI13">
+        <v>6.15</v>
+      </c>
+      <c r="AJ13">
+        <v>1.06</v>
+      </c>
+      <c r="AK13">
+        <v>1.63</v>
+      </c>
+      <c r="AL13">
+        <v>1.97</v>
+      </c>
+      <c r="AM13">
+        <v>1.28</v>
+      </c>
+      <c r="AN13">
+        <v>1.3</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>1.61</v>
+      </c>
+      <c r="AQ13">
+        <v>2.03</v>
+      </c>
+      <c r="AR13">
+        <v>3.48</v>
+      </c>
+      <c r="AS13">
         <v>3.85</v>
       </c>
-      <c r="Y13">
+      <c r="AT13">
+        <v>5.94</v>
+      </c>
+      <c r="AU13">
+        <v>2.16</v>
+      </c>
+      <c r="AV13">
+        <v>1.7</v>
+      </c>
+      <c r="AW13">
+        <v>1.38</v>
+      </c>
+      <c r="AX13">
         <v>1.18</v>
       </c>
-      <c r="Z13">
-        <v>9.6</v>
-      </c>
-      <c r="AA13">
-        <v>1.01</v>
-      </c>
-      <c r="AB13">
-        <v>1.12</v>
-      </c>
-      <c r="AC13">
+      <c r="AY13">
+        <v>1.05</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>1.24</v>
+      </c>
+      <c r="BC13">
+        <v>2.13</v>
+      </c>
+      <c r="BD13">
+        <v>3.6</v>
+      </c>
+      <c r="BE13">
         <v>1.63</v>
       </c>
-      <c r="AD13">
-        <v>2.17</v>
-      </c>
-      <c r="AE13">
-        <v>2.81</v>
-      </c>
-      <c r="AF13">
-        <v>1.33</v>
-      </c>
-      <c r="AG13">
-        <v>5.45</v>
-      </c>
-      <c r="AH13">
-        <v>1.13</v>
-      </c>
-      <c r="AI13">
-        <v>15</v>
-      </c>
-      <c r="AJ13">
-        <v>1.02</v>
-      </c>
-      <c r="AK13">
-        <v>2.27</v>
-      </c>
-      <c r="AL13">
-        <v>1.54</v>
-      </c>
-      <c r="AM13">
-        <v>1.39</v>
-      </c>
-      <c r="AN13">
-        <v>1.5</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>1.66</v>
-      </c>
-      <c r="AQ13">
-        <v>2.05</v>
-      </c>
-      <c r="AR13">
-        <v>3.74</v>
-      </c>
-      <c r="AS13">
-        <v>4.13</v>
-      </c>
-      <c r="AT13">
-        <v>6.49</v>
-      </c>
-      <c r="AU13">
-        <v>2.08</v>
-      </c>
-      <c r="AV13">
-        <v>1.64</v>
-      </c>
-      <c r="AW13">
-        <v>1.34</v>
-      </c>
-      <c r="AX13">
-        <v>1.15</v>
-      </c>
-      <c r="AY13">
-        <v>1.03</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>1.41</v>
-      </c>
-      <c r="BC13">
-        <v>2.9</v>
-      </c>
-      <c r="BD13">
-        <v>2.75</v>
-      </c>
-      <c r="BE13">
-        <v>1.33</v>
-      </c>
       <c r="BF13">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BG13">
         <v>0</v>
@@ -3234,7 +3234,7 @@
         <v>68</v>
       </c>
       <c r="C14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="D14" t="s">
         <v>90</v>
@@ -3246,160 +3246,160 @@
         <v>131</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14">
         <v>2</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
       <c r="J14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>2</v>
       </c>
       <c r="M14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O14" t="s">
         <v>145</v>
       </c>
       <c r="P14">
-        <v>2.86</v>
+        <v>2.1</v>
       </c>
       <c r="Q14">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="R14">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="S14">
-        <v>3.79</v>
+        <v>2.9</v>
       </c>
       <c r="T14">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="U14">
-        <v>2.95</v>
+        <v>4.96</v>
       </c>
       <c r="V14">
+        <v>1.69</v>
+      </c>
+      <c r="W14">
+        <v>2.02</v>
+      </c>
+      <c r="X14">
+        <v>3.85</v>
+      </c>
+      <c r="Y14">
+        <v>1.18</v>
+      </c>
+      <c r="Z14">
+        <v>9.6</v>
+      </c>
+      <c r="AA14">
+        <v>1.01</v>
+      </c>
+      <c r="AB14">
+        <v>1.12</v>
+      </c>
+      <c r="AC14">
+        <v>1.63</v>
+      </c>
+      <c r="AD14">
+        <v>2.17</v>
+      </c>
+      <c r="AE14">
+        <v>2.81</v>
+      </c>
+      <c r="AF14">
+        <v>1.33</v>
+      </c>
+      <c r="AG14">
+        <v>5.45</v>
+      </c>
+      <c r="AH14">
+        <v>1.13</v>
+      </c>
+      <c r="AI14">
+        <v>15</v>
+      </c>
+      <c r="AJ14">
+        <v>1.02</v>
+      </c>
+      <c r="AK14">
+        <v>2.27</v>
+      </c>
+      <c r="AL14">
+        <v>1.54</v>
+      </c>
+      <c r="AM14">
+        <v>1.39</v>
+      </c>
+      <c r="AN14">
+        <v>1.5</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>1.66</v>
+      </c>
+      <c r="AQ14">
+        <v>2.05</v>
+      </c>
+      <c r="AR14">
+        <v>3.74</v>
+      </c>
+      <c r="AS14">
+        <v>4.13</v>
+      </c>
+      <c r="AT14">
+        <v>6.49</v>
+      </c>
+      <c r="AU14">
+        <v>2.08</v>
+      </c>
+      <c r="AV14">
+        <v>1.64</v>
+      </c>
+      <c r="AW14">
+        <v>1.34</v>
+      </c>
+      <c r="AX14">
+        <v>1.15</v>
+      </c>
+      <c r="AY14">
+        <v>1.03</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
         <v>1.41</v>
       </c>
-      <c r="W14">
-        <v>2.59</v>
-      </c>
-      <c r="X14">
-        <v>2.82</v>
-      </c>
-      <c r="Y14">
-        <v>1.35</v>
-      </c>
-      <c r="Z14">
-        <v>7</v>
-      </c>
-      <c r="AA14">
-        <v>1.07</v>
-      </c>
-      <c r="AB14">
-        <v>1.02</v>
-      </c>
-      <c r="AC14">
-        <v>1.28</v>
-      </c>
-      <c r="AD14">
-        <v>3.08</v>
-      </c>
-      <c r="AE14">
-        <v>1.84</v>
-      </c>
-      <c r="AF14">
-        <v>1.75</v>
-      </c>
-      <c r="AG14">
-        <v>3.2</v>
-      </c>
-      <c r="AH14">
-        <v>1.26</v>
-      </c>
-      <c r="AI14">
-        <v>6.15</v>
-      </c>
-      <c r="AJ14">
+      <c r="BC14">
+        <v>2.9</v>
+      </c>
+      <c r="BD14">
+        <v>2.75</v>
+      </c>
+      <c r="BE14">
+        <v>1.33</v>
+      </c>
+      <c r="BF14">
         <v>1.06</v>
-      </c>
-      <c r="AK14">
-        <v>1.63</v>
-      </c>
-      <c r="AL14">
-        <v>1.97</v>
-      </c>
-      <c r="AM14">
-        <v>1.28</v>
-      </c>
-      <c r="AN14">
-        <v>1.3</v>
-      </c>
-      <c r="AO14">
-        <v>0</v>
-      </c>
-      <c r="AP14">
-        <v>1.61</v>
-      </c>
-      <c r="AQ14">
-        <v>2.03</v>
-      </c>
-      <c r="AR14">
-        <v>3.48</v>
-      </c>
-      <c r="AS14">
-        <v>3.85</v>
-      </c>
-      <c r="AT14">
-        <v>5.94</v>
-      </c>
-      <c r="AU14">
-        <v>2.16</v>
-      </c>
-      <c r="AV14">
-        <v>1.7</v>
-      </c>
-      <c r="AW14">
-        <v>1.38</v>
-      </c>
-      <c r="AX14">
-        <v>1.18</v>
-      </c>
-      <c r="AY14">
-        <v>1.05</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.24</v>
-      </c>
-      <c r="BC14">
-        <v>2.13</v>
-      </c>
-      <c r="BD14">
-        <v>3.6</v>
-      </c>
-      <c r="BE14">
-        <v>1.63</v>
-      </c>
-      <c r="BF14">
-        <v>1.16</v>
       </c>
       <c r="BG14">
         <v>0</v>
@@ -3616,160 +3616,160 @@
         <v>133</v>
       </c>
       <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>3</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
         <v>2</v>
       </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>2</v>
-      </c>
-      <c r="L16">
-        <v>1</v>
-      </c>
       <c r="M16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N16">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O16" t="s">
         <v>145</v>
       </c>
       <c r="P16">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q16">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="R16">
-        <v>1.71</v>
+        <v>1.85</v>
       </c>
       <c r="S16">
-        <v>4.45</v>
+        <v>4.2</v>
       </c>
       <c r="T16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="U16">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="V16">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="W16">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="X16">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="Y16">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z16">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="AA16">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AB16">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC16">
         <v>1.2</v>
       </c>
       <c r="AD16">
-        <v>3.7</v>
+        <v>4.25</v>
       </c>
       <c r="AE16">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AF16">
-        <v>1.96</v>
+        <v>2.23</v>
       </c>
       <c r="AG16">
-        <v>2.91</v>
+        <v>2.38</v>
       </c>
       <c r="AH16">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI16">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AJ16">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK16">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="AL16">
+        <v>2.19</v>
+      </c>
+      <c r="AM16">
+        <v>1.23</v>
+      </c>
+      <c r="AN16">
+        <v>1.23</v>
+      </c>
+      <c r="AO16">
+        <v>0</v>
+      </c>
+      <c r="AP16">
+        <v>1.34</v>
+      </c>
+      <c r="AQ16">
+        <v>1.47</v>
+      </c>
+      <c r="AR16">
         <v>2.04</v>
       </c>
-      <c r="AM16">
-        <v>1.19</v>
-      </c>
-      <c r="AN16">
-        <v>1.16</v>
-      </c>
-      <c r="AO16">
-        <v>0</v>
-      </c>
-      <c r="AP16">
-        <v>1.37</v>
-      </c>
-      <c r="AQ16">
-        <v>1.7</v>
-      </c>
-      <c r="AR16">
-        <v>2.54</v>
-      </c>
       <c r="AS16">
-        <v>2.83</v>
+        <v>2.35</v>
       </c>
       <c r="AT16">
-        <v>4.03</v>
+        <v>3.41</v>
       </c>
       <c r="AU16">
-        <v>2.71</v>
+        <v>2.98</v>
       </c>
       <c r="AV16">
-        <v>2.03</v>
+        <v>2.19</v>
       </c>
       <c r="AW16">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AX16">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="AY16">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BB16">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="BC16">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="BD16">
-        <v>4.05</v>
+        <v>4.55</v>
       </c>
       <c r="BE16">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="BF16">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BG16">
         <v>0</v>
@@ -3792,7 +3792,7 @@
         <v>84</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E17" t="s">
         <v>108</v>
@@ -3801,160 +3801,160 @@
         <v>134</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M17">
         <v>5</v>
       </c>
       <c r="N17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="s">
         <v>145</v>
       </c>
       <c r="P17">
+        <v>1.29</v>
+      </c>
+      <c r="Q17">
+        <v>5</v>
+      </c>
+      <c r="R17">
+        <v>7.85</v>
+      </c>
+      <c r="S17">
+        <v>1.74</v>
+      </c>
+      <c r="T17">
+        <v>2.61</v>
+      </c>
+      <c r="U17">
+        <v>6.75</v>
+      </c>
+      <c r="V17">
+        <v>1.18</v>
+      </c>
+      <c r="W17">
         <v>3.85</v>
       </c>
-      <c r="Q17">
-        <v>3.8</v>
-      </c>
-      <c r="R17">
-        <v>1.85</v>
-      </c>
-      <c r="S17">
-        <v>4.2</v>
-      </c>
-      <c r="T17">
-        <v>2.26</v>
-      </c>
-      <c r="U17">
-        <v>2.32</v>
-      </c>
-      <c r="V17">
-        <v>1.27</v>
-      </c>
-      <c r="W17">
-        <v>3.25</v>
-      </c>
       <c r="X17">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="Y17">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="Z17">
-        <v>5.3</v>
+        <v>4.25</v>
       </c>
       <c r="AA17">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AB17">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AC17">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AD17">
-        <v>4.25</v>
+        <v>6</v>
       </c>
       <c r="AE17">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AF17">
-        <v>2.23</v>
+        <v>2.74</v>
       </c>
       <c r="AG17">
-        <v>2.38</v>
+        <v>2.01</v>
       </c>
       <c r="AH17">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AI17">
-        <v>4.25</v>
+        <v>3.1</v>
       </c>
       <c r="AJ17">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AL17">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="AM17">
-        <v>1.23</v>
+        <v>1.1</v>
       </c>
       <c r="AN17">
-        <v>1.23</v>
+        <v>3.02</v>
       </c>
       <c r="AO17">
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="AQ17">
-        <v>1.47</v>
+        <v>1.19</v>
       </c>
       <c r="AR17">
+        <v>1.43</v>
+      </c>
+      <c r="AS17">
+        <v>1.69</v>
+      </c>
+      <c r="AT17">
+        <v>2.08</v>
+      </c>
+      <c r="AU17">
+        <v>5.87</v>
+      </c>
+      <c r="AV17">
+        <v>3.4</v>
+      </c>
+      <c r="AW17">
+        <v>2.55</v>
+      </c>
+      <c r="AX17">
         <v>2.04</v>
       </c>
-      <c r="AS17">
-        <v>2.35</v>
-      </c>
-      <c r="AT17">
-        <v>3.41</v>
-      </c>
-      <c r="AU17">
-        <v>2.98</v>
-      </c>
-      <c r="AV17">
-        <v>2.19</v>
-      </c>
-      <c r="AW17">
-        <v>1.82</v>
-      </c>
-      <c r="AX17">
-        <v>1.47</v>
-      </c>
       <c r="AY17">
+        <v>1.65</v>
+      </c>
+      <c r="AZ17">
         <v>1.25</v>
       </c>
-      <c r="AZ17">
-        <v>2.38</v>
-      </c>
       <c r="BA17">
-        <v>1.9</v>
+        <v>4.35</v>
       </c>
       <c r="BB17">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BC17">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="BD17">
-        <v>4.55</v>
+        <v>6.1</v>
       </c>
       <c r="BE17">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="BF17">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="BG17">
         <v>0</v>
@@ -3977,7 +3977,7 @@
         <v>85</v>
       </c>
       <c r="D18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
         <v>109</v>
@@ -3986,160 +3986,160 @@
         <v>135</v>
       </c>
       <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>2</v>
+      </c>
+      <c r="L18">
+        <v>1</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
         <v>5</v>
-      </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18">
-        <v>4</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>1</v>
-      </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>5</v>
-      </c>
-      <c r="N18">
-        <v>0</v>
       </c>
       <c r="O18" t="s">
         <v>145</v>
       </c>
       <c r="P18">
-        <v>1.29</v>
+        <v>4</v>
       </c>
       <c r="Q18">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="R18">
-        <v>7.85</v>
+        <v>1.71</v>
       </c>
       <c r="S18">
+        <v>4.45</v>
+      </c>
+      <c r="T18">
+        <v>2.28</v>
+      </c>
+      <c r="U18">
+        <v>2.45</v>
+      </c>
+      <c r="V18">
+        <v>1.36</v>
+      </c>
+      <c r="W18">
+        <v>2.8</v>
+      </c>
+      <c r="X18">
+        <v>2.53</v>
+      </c>
+      <c r="Y18">
+        <v>1.42</v>
+      </c>
+      <c r="Z18">
+        <v>7</v>
+      </c>
+      <c r="AA18">
+        <v>1.06</v>
+      </c>
+      <c r="AB18">
+        <v>1.04</v>
+      </c>
+      <c r="AC18">
+        <v>1.2</v>
+      </c>
+      <c r="AD18">
+        <v>3.7</v>
+      </c>
+      <c r="AE18">
+        <v>1.76</v>
+      </c>
+      <c r="AF18">
+        <v>1.96</v>
+      </c>
+      <c r="AG18">
+        <v>2.91</v>
+      </c>
+      <c r="AH18">
+        <v>1.33</v>
+      </c>
+      <c r="AI18">
+        <v>4.6</v>
+      </c>
+      <c r="AJ18">
+        <v>1.09</v>
+      </c>
+      <c r="AK18">
+        <v>1.67</v>
+      </c>
+      <c r="AL18">
+        <v>2.04</v>
+      </c>
+      <c r="AM18">
+        <v>1.19</v>
+      </c>
+      <c r="AN18">
+        <v>1.16</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>1.37</v>
+      </c>
+      <c r="AQ18">
+        <v>1.7</v>
+      </c>
+      <c r="AR18">
+        <v>2.54</v>
+      </c>
+      <c r="AS18">
+        <v>2.83</v>
+      </c>
+      <c r="AT18">
+        <v>4.03</v>
+      </c>
+      <c r="AU18">
+        <v>2.71</v>
+      </c>
+      <c r="AV18">
+        <v>2.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.62</v>
+      </c>
+      <c r="AX18">
+        <v>1.34</v>
+      </c>
+      <c r="AY18">
+        <v>1.16</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>1.16</v>
+      </c>
+      <c r="BC18">
+        <v>2</v>
+      </c>
+      <c r="BD18">
+        <v>4.05</v>
+      </c>
+      <c r="BE18">
         <v>1.74</v>
       </c>
-      <c r="T18">
-        <v>2.61</v>
-      </c>
-      <c r="U18">
-        <v>6.75</v>
-      </c>
-      <c r="V18">
-        <v>1.18</v>
-      </c>
-      <c r="W18">
-        <v>3.85</v>
-      </c>
-      <c r="X18">
-        <v>2.02</v>
-      </c>
-      <c r="Y18">
-        <v>1.7</v>
-      </c>
-      <c r="Z18">
-        <v>4.25</v>
-      </c>
-      <c r="AA18">
-        <v>1.15</v>
-      </c>
-      <c r="AB18">
-        <v>1.01</v>
-      </c>
-      <c r="AC18">
-        <v>1.08</v>
-      </c>
-      <c r="AD18">
-        <v>6</v>
-      </c>
-      <c r="AE18">
-        <v>1.35</v>
-      </c>
-      <c r="AF18">
-        <v>2.74</v>
-      </c>
-      <c r="AG18">
-        <v>2.01</v>
-      </c>
-      <c r="AH18">
-        <v>1.75</v>
-      </c>
-      <c r="AI18">
-        <v>3.1</v>
-      </c>
-      <c r="AJ18">
-        <v>1.28</v>
-      </c>
-      <c r="AK18">
-        <v>1.6</v>
-      </c>
-      <c r="AL18">
-        <v>2.18</v>
-      </c>
-      <c r="AM18">
-        <v>1.1</v>
-      </c>
-      <c r="AN18">
-        <v>3.02</v>
-      </c>
-      <c r="AO18">
-        <v>0</v>
-      </c>
-      <c r="AP18">
-        <v>1.05</v>
-      </c>
-      <c r="AQ18">
-        <v>1.19</v>
-      </c>
-      <c r="AR18">
-        <v>1.43</v>
-      </c>
-      <c r="AS18">
-        <v>1.69</v>
-      </c>
-      <c r="AT18">
-        <v>2.08</v>
-      </c>
-      <c r="AU18">
-        <v>5.87</v>
-      </c>
-      <c r="AV18">
-        <v>3.4</v>
-      </c>
-      <c r="AW18">
-        <v>2.55</v>
-      </c>
-      <c r="AX18">
-        <v>2.04</v>
-      </c>
-      <c r="AY18">
-        <v>1.65</v>
-      </c>
-      <c r="AZ18">
-        <v>1.25</v>
-      </c>
-      <c r="BA18">
-        <v>4.35</v>
-      </c>
-      <c r="BB18">
-        <v>1.09</v>
-      </c>
-      <c r="BC18">
-        <v>1.56</v>
-      </c>
-      <c r="BD18">
-        <v>6.1</v>
-      </c>
-      <c r="BE18">
-        <v>2.2</v>
-      </c>
       <c r="BF18">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="BG18">
         <v>0</v>
@@ -4344,10 +4344,10 @@
         <v>71</v>
       </c>
       <c r="C20" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E20" t="s">
         <v>111</v>
@@ -4356,160 +4356,160 @@
         <v>137</v>
       </c>
       <c r="G20">
+        <v>5</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>2</v>
       </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
       <c r="J20">
         <v>0</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="N20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O20" t="s">
         <v>145</v>
       </c>
       <c r="P20">
-        <v>2.3</v>
+        <v>1.08</v>
       </c>
       <c r="Q20">
-        <v>2.98</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>3.11</v>
+        <v>18</v>
       </c>
       <c r="S20">
-        <v>3.14</v>
+        <v>1.36</v>
       </c>
       <c r="T20">
-        <v>1.82</v>
+        <v>3.45</v>
       </c>
       <c r="U20">
-        <v>3.67</v>
+        <v>12.5</v>
       </c>
       <c r="V20">
-        <v>1.5</v>
+        <v>1.15</v>
       </c>
       <c r="W20">
-        <v>2.17</v>
+        <v>5</v>
       </c>
       <c r="X20">
-        <v>3.4</v>
+        <v>1.76</v>
       </c>
       <c r="Y20">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="Z20">
-        <v>11</v>
+        <v>3.28</v>
       </c>
       <c r="AA20">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
       <c r="AB20">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AC20">
-        <v>1.5</v>
+        <v>1.06</v>
       </c>
       <c r="AD20">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AE20">
+        <v>1.19</v>
+      </c>
+      <c r="AF20">
+        <v>3.88</v>
+      </c>
+      <c r="AG20">
+        <v>1.57</v>
+      </c>
+      <c r="AH20">
         <v>2.32</v>
       </c>
-      <c r="AE20">
-        <v>2.6</v>
-      </c>
-      <c r="AF20">
+      <c r="AI20">
+        <v>2.23</v>
+      </c>
+      <c r="AJ20">
+        <v>1.53</v>
+      </c>
+      <c r="AK20">
+        <v>1.93</v>
+      </c>
+      <c r="AL20">
+        <v>1.78</v>
+      </c>
+      <c r="AM20">
+        <v>1.03</v>
+      </c>
+      <c r="AN20">
+        <v>7.1</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>1.2</v>
+      </c>
+      <c r="AQ20">
+        <v>1.37</v>
+      </c>
+      <c r="AR20">
+        <v>1.81</v>
+      </c>
+      <c r="AS20">
+        <v>1.98</v>
+      </c>
+      <c r="AT20">
+        <v>2.43</v>
+      </c>
+      <c r="AU20">
+        <v>3.9</v>
+      </c>
+      <c r="AV20">
+        <v>2.36</v>
+      </c>
+      <c r="AW20">
+        <v>2.14</v>
+      </c>
+      <c r="AX20">
+        <v>1.78</v>
+      </c>
+      <c r="AY20">
         <v>1.44</v>
       </c>
-      <c r="AG20">
-        <v>4.95</v>
-      </c>
-      <c r="AH20">
-        <v>1.18</v>
-      </c>
-      <c r="AI20">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="AJ20">
-        <v>1</v>
-      </c>
-      <c r="AK20">
-        <v>2.14</v>
-      </c>
-      <c r="AL20">
-        <v>1.62</v>
-      </c>
-      <c r="AM20">
-        <v>1.34</v>
-      </c>
-      <c r="AN20">
-        <v>1.48</v>
-      </c>
-      <c r="AO20">
-        <v>0</v>
-      </c>
-      <c r="AP20">
-        <v>1.36</v>
-      </c>
-      <c r="AQ20">
-        <v>1.67</v>
-      </c>
-      <c r="AR20">
-        <v>2.48</v>
-      </c>
-      <c r="AS20">
-        <v>2.77</v>
-      </c>
-      <c r="AT20">
-        <v>3.91</v>
-      </c>
-      <c r="AU20">
-        <v>2.77</v>
-      </c>
-      <c r="AV20">
-        <v>2.07</v>
-      </c>
-      <c r="AW20">
-        <v>1.65</v>
-      </c>
-      <c r="AX20">
-        <v>1.36</v>
-      </c>
-      <c r="AY20">
-        <v>1.17</v>
-      </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BB20">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="BC20">
-        <v>2.75</v>
+        <v>1.38</v>
       </c>
       <c r="BD20">
-        <v>2.78</v>
+        <v>7.8</v>
       </c>
       <c r="BE20">
-        <v>1.42</v>
+        <v>2.81</v>
       </c>
       <c r="BF20">
-        <v>1.08</v>
+        <v>1.6</v>
       </c>
       <c r="BG20">
         <v>0</v>
@@ -4529,10 +4529,10 @@
         <v>71</v>
       </c>
       <c r="C21" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
         <v>112</v>
@@ -4541,160 +4541,160 @@
         <v>138</v>
       </c>
       <c r="G21">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
         <v>2</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>3</v>
-      </c>
       <c r="L21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M21">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="N21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O21" t="s">
         <v>145</v>
       </c>
       <c r="P21">
+        <v>2.3</v>
+      </c>
+      <c r="Q21">
+        <v>2.98</v>
+      </c>
+      <c r="R21">
+        <v>3.11</v>
+      </c>
+      <c r="S21">
+        <v>3.14</v>
+      </c>
+      <c r="T21">
+        <v>1.82</v>
+      </c>
+      <c r="U21">
+        <v>3.67</v>
+      </c>
+      <c r="V21">
+        <v>1.5</v>
+      </c>
+      <c r="W21">
+        <v>2.17</v>
+      </c>
+      <c r="X21">
+        <v>3.4</v>
+      </c>
+      <c r="Y21">
+        <v>1.21</v>
+      </c>
+      <c r="Z21">
+        <v>11</v>
+      </c>
+      <c r="AA21">
+        <v>1.02</v>
+      </c>
+      <c r="AB21">
         <v>1.08</v>
       </c>
-      <c r="Q21">
-        <v>10</v>
-      </c>
-      <c r="R21">
-        <v>18</v>
-      </c>
-      <c r="S21">
+      <c r="AC21">
+        <v>1.5</v>
+      </c>
+      <c r="AD21">
+        <v>2.32</v>
+      </c>
+      <c r="AE21">
+        <v>2.6</v>
+      </c>
+      <c r="AF21">
+        <v>1.44</v>
+      </c>
+      <c r="AG21">
+        <v>4.95</v>
+      </c>
+      <c r="AH21">
+        <v>1.18</v>
+      </c>
+      <c r="AI21">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="AJ21">
+        <v>1</v>
+      </c>
+      <c r="AK21">
+        <v>2.14</v>
+      </c>
+      <c r="AL21">
+        <v>1.62</v>
+      </c>
+      <c r="AM21">
+        <v>1.34</v>
+      </c>
+      <c r="AN21">
+        <v>1.48</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
         <v>1.36</v>
       </c>
-      <c r="T21">
-        <v>3.45</v>
-      </c>
-      <c r="U21">
-        <v>12.5</v>
-      </c>
-      <c r="V21">
-        <v>1.15</v>
-      </c>
-      <c r="W21">
-        <v>5</v>
-      </c>
-      <c r="X21">
-        <v>1.76</v>
-      </c>
-      <c r="Y21">
-        <v>2</v>
-      </c>
-      <c r="Z21">
-        <v>3.28</v>
-      </c>
-      <c r="AA21">
-        <v>1.27</v>
-      </c>
-      <c r="AB21">
-        <v>1</v>
-      </c>
-      <c r="AC21">
-        <v>1.06</v>
-      </c>
-      <c r="AD21">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AE21">
-        <v>1.19</v>
-      </c>
-      <c r="AF21">
-        <v>3.88</v>
-      </c>
-      <c r="AG21">
-        <v>1.57</v>
-      </c>
-      <c r="AH21">
-        <v>2.32</v>
-      </c>
-      <c r="AI21">
-        <v>2.23</v>
-      </c>
-      <c r="AJ21">
-        <v>1.53</v>
-      </c>
-      <c r="AK21">
-        <v>1.93</v>
-      </c>
-      <c r="AL21">
-        <v>1.78</v>
-      </c>
-      <c r="AM21">
-        <v>1.03</v>
-      </c>
-      <c r="AN21">
-        <v>7.1</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>1.2</v>
-      </c>
       <c r="AQ21">
-        <v>1.37</v>
+        <v>1.67</v>
       </c>
       <c r="AR21">
-        <v>1.81</v>
+        <v>2.48</v>
       </c>
       <c r="AS21">
-        <v>1.98</v>
+        <v>2.77</v>
       </c>
       <c r="AT21">
-        <v>2.43</v>
+        <v>3.91</v>
       </c>
       <c r="AU21">
-        <v>3.9</v>
+        <v>2.77</v>
       </c>
       <c r="AV21">
-        <v>2.36</v>
+        <v>2.07</v>
       </c>
       <c r="AW21">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="AX21">
-        <v>1.78</v>
+        <v>1.36</v>
       </c>
       <c r="AY21">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="AZ21">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="BA21">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BB21">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="BC21">
-        <v>1.38</v>
+        <v>2.75</v>
       </c>
       <c r="BD21">
-        <v>7.8</v>
+        <v>2.78</v>
       </c>
       <c r="BE21">
-        <v>2.81</v>
+        <v>1.42</v>
       </c>
       <c r="BF21">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="BG21">
         <v>0</v>
@@ -5084,7 +5084,7 @@
         <v>73</v>
       </c>
       <c r="C24" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D24" t="s">
         <v>90</v>
